--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>445.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-598.9%</t>
+          <t>-599.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-269.8%</t>
+          <t>-270.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-294.4%</t>
+          <t>-282.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-214.6%</t>
+          <t>-197.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.0%</t>
+          <t>-148.7%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386097</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998565</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082129</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776673</v>
+        <v>3.500446096776672</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792545</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628923</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675893</v>
+        <v>3.746038950675891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695438</v>
+        <v>3.765020747695436</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273186</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.158503103490178</v>
+        <v>-4.307521613674616</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.139595129197701</v>
+        <v>1.079987725123926</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.186898458418909</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.065692622039318</v>
+        <v>-4.214711132223757</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.105992013669411</v>
+        <v>1.046384609595635</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.0940879769680496</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.017129569818288</v>
+        <v>-4.166148080002727</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.127290710482423</v>
+        <v>1.067683306408648</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.04552492474701941</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.904458351582038</v>
+        <v>-4.053476861766477</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.167434906288647</v>
+        <v>1.107827502214871</v>
       </c>
       <c r="F1948" t="n">
         <v>0.06714629348923079</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268533</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.792081350399366</v>
+        <v>-3.941099860583804</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.217877002592383</v>
+        <v>1.158269598518607</v>
       </c>
       <c r="F1949" t="n">
         <v>0.06714629348923079</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.990315919286096</v>
+        <v>-4.139334429470535</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.15008037680623</v>
+        <v>1.090472972732454</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1310882753974998</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175319</v>
+        <v>3.643066046175317</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.073317200311375</v>
+        <v>-4.222335710495813</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9552355843967715</v>
+        <v>0.895628180322996</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1496591599246735</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199264</v>
+        <v>3.682712735199262</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.200384206618363</v>
+        <v>-4.349402716802802</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.024558442593182</v>
+        <v>0.9649510385194064</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1496591599246735</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.733008865660761</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.286982789599466</v>
+        <v>-4.436001299783904</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.004432035503064</v>
+        <v>0.9448246314292883</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1496591599246735</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383418</v>
+        <v>3.741170494383416</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.248599127041315</v>
+        <v>-4.397617637225753</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.017204941868693</v>
+        <v>0.9575975377949173</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1112754973665224</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002479</v>
+        <v>3.751143622002477</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.071482797006149</v>
+        <v>-4.220501307190587</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.084780502728061</v>
+        <v>1.025173098654286</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1112754973665224</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263896</v>
+        <v>3.741324873263894</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.041780673029855</v>
+        <v>-4.190799183214294</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.097344744080492</v>
+        <v>1.037737340006716</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1157456225818357</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481228</v>
+        <v>3.750725801481226</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.862405251791087</v>
+        <v>-4.011423761975526</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.162881887882413</v>
+        <v>1.103274483808638</v>
       </c>
       <c r="F1957" t="n">
         <v>0.04103113558888294</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452223</v>
+        <v>3.716988143452221</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.907419465311694</v>
+        <v>-4.056437975496133</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.125683657805761</v>
+        <v>1.066076253731985</v>
       </c>
       <c r="F1958" t="n">
         <v>0.01068224027427833</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979527</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.174423975584129</v>
+        <v>-4.323442485768568</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.024573416035732</v>
+        <v>0.9649660119619565</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1836807977686702</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230803</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.463211196043044</v>
+        <v>-4.612229706227483</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9082624497486673</v>
+        <v>0.8486550456748918</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2847669178676706</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.430735609872272</v>
+        <v>-4.579754120056711</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9188526457712929</v>
+        <v>0.8592452416975176</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2847669178676706</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.411697482164975</v>
+        <v>-4.560715992349413</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9229926160624569</v>
+        <v>0.8633852119886813</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3429505291988652</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.442824113315593</v>
+        <v>-4.591842623500032</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.08812383254089</v>
+        <v>1.028516428467114</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3429505291988652</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.495144493916385</v>
+        <v>-4.644163004100823</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.068029009286707</v>
+        <v>1.008421605212931</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.308003669189993</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259117</v>
+        <v>3.787422005259115</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.639467399841304</v>
+        <v>-4.788485910025742</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.016308377313665</v>
+        <v>0.9567009732398897</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.308003669189993</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989902</v>
+        <v>3.7814976749899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.491724429606301</v>
+        <v>-4.64074293979074</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.154558213199688</v>
+        <v>1.094950809125913</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1401963119551098</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651163</v>
+        <v>3.802242353651161</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.593739112137523</v>
+        <v>-4.742757622321961</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.116545961718681</v>
+        <v>1.056938557644905</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1401963119551098</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864722</v>
+        <v>3.80560540986472</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.45712976804343</v>
+        <v>-4.606148278227868</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.171852047747976</v>
+        <v>1.112244643674201</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.003586967861017365</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360611</v>
+        <v>3.798236219360607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.59989510086608</v>
+        <v>-4.748913611050519</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.113826391359026</v>
+        <v>1.054218987285251</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.1463523006836678</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86735906126842</v>
+        <v>3.867359061268418</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.537597102089958</v>
+        <v>-4.686615612274396</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.205081144666296</v>
+        <v>1.145473740592521</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.1463523006836678</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462184</v>
+        <v>3.848725564462182</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.3358069044248</v>
+        <v>-4.484825414609238</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9943780961217572</v>
+        <v>0.9347706920479819</v>
       </c>
       <c r="F1971" t="n">
         <v>0.05166589148548661</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322418</v>
+        <v>3.841441242322416</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.275916222782207</v>
+        <v>-4.424934732966645</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.08862460110097</v>
+        <v>1.029017197027194</v>
       </c>
       <c r="F1972" t="n">
         <v>0.1115565731280801</v>
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.849506197408475</v>
+        <v>3.474569591860634</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.373055227661496</v>
+        <v>-4.381121508563551</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.064396735265298</v>
+        <v>1.061170222904476</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.09405151353739255</v>
+        <v>0.2657020010945181</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.870406158766079</v>
+        <v>2.973396451300355</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.2%</t>
+          <t>445.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.7%</t>
+          <t>-610.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.1%</t>
+          <t>-274.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-282.1%</t>
+          <t>-234.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-197.4%</t>
+          <t>-226.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-148.7%</t>
+          <t>-166.0%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706676</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.299918119296843</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201493</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153012</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537431</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382196</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776672</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.746038950675893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695436</v>
+        <v>3.765020747695438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273186</v>
+        <v>3.753567590273188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.307521613674616</v>
+        <v>-4.158503103490178</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.079987725123926</v>
+        <v>1.139595129197701</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.186898458418909</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.214711132223757</v>
+        <v>-4.184901365251918</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.046384609595635</v>
+        <v>1.058308516384371</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.0940879769680496</v>
+        <v>-0.2132967201806493</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.676172700618056</v>
+        <v>2.604647454690496</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030423</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.166148080002727</v>
+        <v>-4.136338313030889</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.067683306408648</v>
+        <v>1.079607213197384</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.04552492474701941</v>
+        <v>-0.1647336679596191</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.707184007875275</v>
+        <v>2.635658761947715</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942735</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.053476861766477</v>
+        <v>-4.023667094794638</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.107827502214871</v>
+        <v>1.119751409003606</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.06714629348923079</v>
+        <v>-0.05206244972336888</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.769862447328748</v>
+        <v>2.698337201401188</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268533</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.941099860583804</v>
+        <v>-3.911290093611966</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.158269598518607</v>
+        <v>1.170193505307343</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.06714629348923079</v>
+        <v>-0.05206244972336888</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.775353743159415</v>
+        <v>2.703828497231855</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.139334429470535</v>
+        <v>-4.109524662498696</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.090472972732454</v>
+        <v>1.10239687952119</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1310882753974998</v>
+        <v>-0.2502970186100995</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.667910203595916</v>
+        <v>2.596384957668356</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175317</v>
+        <v>3.643066046175319</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.222335710495813</v>
+        <v>-4.192525943523975</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.895628180322996</v>
+        <v>0.9075520871117313</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1496591599246735</v>
+        <v>-0.2688679031372732</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.495123392880265</v>
+        <v>2.423598146952705</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199262</v>
+        <v>3.682712735199264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.349402716802802</v>
+        <v>-4.319592949830963</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9649510385194064</v>
+        <v>0.9768749453081418</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1496591599246735</v>
+        <v>-0.2688679031372732</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.61527305359947</v>
+        <v>2.543747807671911</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660761</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.436001299783904</v>
+        <v>-4.406191532812066</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9448246314292883</v>
+        <v>0.9567485382180236</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1496591599246735</v>
+        <v>-0.2688679031372732</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.629786079701793</v>
+        <v>2.558260833774234</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383416</v>
+        <v>3.741170494383418</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.397617637225753</v>
+        <v>-4.367807870253915</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9575975377949173</v>
+        <v>0.9695214445836526</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1112754973665224</v>
+        <v>-0.230484240579122</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.650235718579053</v>
+        <v>2.578710472651493</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002477</v>
+        <v>3.751143622002479</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.220501307190587</v>
+        <v>-4.190691540218749</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025173098654286</v>
+        <v>1.037097005443021</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1112754973665224</v>
+        <v>-0.230484240579122</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.646964747424355</v>
+        <v>2.575439501496795</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263894</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.190799183214294</v>
+        <v>-4.160989416242455</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.037737340006716</v>
+        <v>1.049661246795452</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1157456225818357</v>
+        <v>-0.2349543657944354</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.64496606405708</v>
+        <v>2.57344081812952</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481226</v>
+        <v>3.750725801481228</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.011423761975526</v>
+        <v>-3.981613995003688</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.103274483808638</v>
+        <v>1.115198390597373</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04103113558888294</v>
+        <v>-0.07817760762371673</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.732819094265925</v>
+        <v>2.661293848338365</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452221</v>
+        <v>3.716988143452223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.056437975496133</v>
+        <v>-4.026628208524293</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.066076253731985</v>
+        <v>1.078000160520721</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01068224027427833</v>
+        <v>-0.1085265029383213</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.695417212408752</v>
+        <v>2.623891966481192</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979527</v>
+        <v>3.737023032979529</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.323442485768568</v>
+        <v>-4.293632718796728</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9649660119619565</v>
+        <v>0.9768899187506923</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1836807977686702</v>
+        <v>-0.3028895409812699</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.584490951921929</v>
+        <v>2.512965705994369</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230803</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.612229706227483</v>
+        <v>-4.582419939255644</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8486550456748918</v>
+        <v>0.8605789524636276</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2847669178676706</v>
+        <v>-0.4039756610802703</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.52304320175903</v>
+        <v>2.45151795583147</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285449</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.579754120056711</v>
+        <v>-4.549944353084872</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8592452416975176</v>
+        <v>0.8711691484862532</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2847669178676706</v>
+        <v>-0.4039756610802703</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.520643163313347</v>
+        <v>2.449117917385787</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.560715992349413</v>
+        <v>-4.530906225377574</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8633852119886813</v>
+        <v>0.8753091187774169</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3429505291988652</v>
+        <v>-0.4621592724114648</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.482257715722875</v>
+        <v>2.410732469795315</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.591842623500032</v>
+        <v>-4.562032856528193</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.028516428467114</v>
+        <v>1.04044033525585</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3429505291988652</v>
+        <v>-0.4621592724114648</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.659839584661556</v>
+        <v>2.588314338733996</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537859</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.644163004100823</v>
+        <v>-4.614353237128984</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.008421605212931</v>
+        <v>1.020345512001667</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.308003669189993</v>
+        <v>-0.4272124124025927</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.681641029653012</v>
+        <v>2.610115783725453</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259115</v>
+        <v>3.787422005259118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.788485910025742</v>
+        <v>-4.758676143053903</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9567009732398897</v>
+        <v>0.9686248800286255</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.308003669189993</v>
+        <v>-0.4272124124025927</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.687649560049938</v>
+        <v>2.616124314122379</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.7814976749899</v>
+        <v>3.781497674989903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.64074293979074</v>
+        <v>-4.610933172818901</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.094950809125913</v>
+        <v>1.106874715914648</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1401963119551098</v>
+        <v>-0.2594050551677095</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.86748662218289</v>
+        <v>2.795961376255331</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651161</v>
+        <v>3.802242353651165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.742757622321961</v>
+        <v>-4.712947855350122</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.056938557644905</v>
+        <v>1.068862464433641</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1401963119551098</v>
+        <v>-0.2594050551677095</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.870280243714371</v>
+        <v>2.798754997786812</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560540986472</v>
+        <v>3.805605409864723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.606148278227868</v>
+        <v>-4.576338511256029</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.112244643674201</v>
+        <v>1.124168550462936</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.003586967861017365</v>
+        <v>-0.122795711073617</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.952908198562485</v>
+        <v>2.881382952634925</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360607</v>
+        <v>3.798236219360613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.748913611050519</v>
+        <v>-4.719103844078679</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.054218987285251</v>
+        <v>1.066142894073987</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1463523006836678</v>
+        <v>-0.2655610438962674</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.866329475609005</v>
+        <v>2.794804229681445</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268418</v>
+        <v>3.867359061268422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.686615612274396</v>
+        <v>-4.656805845302557</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.145473740592521</v>
+        <v>1.157397647381256</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1463523006836678</v>
+        <v>-0.2655610438962674</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.932665029405826</v>
+        <v>2.861139783478266</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462182</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.484825414609238</v>
+        <v>-4.455015647637399</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9347706920479819</v>
+        <v>0.9466945988367175</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.05166589148548661</v>
+        <v>-0.06754285172711305</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.760056817096717</v>
+        <v>2.688531571169157</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322416</v>
+        <v>3.84144124232242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.424934732966645</v>
+        <v>-4.395124965994806</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.029017197027194</v>
+        <v>1.04094110381593</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1115565731280801</v>
+        <v>-0.007652170084519572</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.866281458404448</v>
+        <v>2.794756212476888</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.474569591860634</v>
+        <v>3.517519711190525</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.381121508563551</v>
+        <v>-4.49286551061978</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.061170222904476</v>
+        <v>1.016472622081984</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2657020010945181</v>
+        <v>-0.02354144821749976</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.973396451300355</v>
+        <v>2.799850381713143</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.5%</t>
+          <t>445.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.9%</t>
+          <t>-621.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-274.6%</t>
+          <t>-279.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-234.1%</t>
+          <t>-99.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.3%</t>
+          <t>-224.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.0%</t>
+          <t>-164.9%</t>
         </is>
       </c>
     </row>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860589</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.492098065767403</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792545</v>
+        <v>3.573670449792547</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628923</v>
+        <v>3.600034689628925</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487765</v>
+        <v>3.789307536487767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858721</v>
+        <v>3.839370871858723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096466</v>
+        <v>3.856158176096468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.486893469543269</v>
+        <v>-7.586856026190845</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1560341928309414</v>
+        <v>0.1160491701719106</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.250436704010897</v>
+        <v>-1.350399260658475</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.400885982555458</v>
+        <v>2.340908448566912</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.237893670859687</v>
+        <v>-7.337856227507264</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2685404535280327</v>
+        <v>0.2285554308690019</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.250436704010897</v>
+        <v>-1.350399260658475</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.413792323779117</v>
+        <v>2.353814789790571</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.343483660632792</v>
+        <v>-7.443446217280369</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.09832852801957204</v>
+        <v>0.05834350536054167</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.356026693784002</v>
+        <v>-1.455989250431579</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.222462400316036</v>
+        <v>2.162484866327489</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.362218562751389</v>
+        <v>-7.462181119398966</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1393789090492197</v>
+        <v>0.09939388639018887</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.356026693784002</v>
+        <v>-1.455989250431579</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.271006742193122</v>
+        <v>2.211029208204575</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.21427852134379</v>
+        <v>-7.314241077991366</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07867600292409183</v>
+        <v>0.03869098026506101</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.335705777875444</v>
+        <v>-1.435668334523021</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.163320369050089</v>
+        <v>2.103342835061543</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.197120371212495</v>
+        <v>-7.297082927860072</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07682527672313144</v>
+        <v>0.03684025406410063</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.418510184391727</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.164901272875387</v>
+        <v>2.104923738886841</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.153571964441805</v>
+        <v>-7.253534521089382</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08728402733631446</v>
+        <v>0.04729900467728365</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.418510184391727</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.157940660780294</v>
+        <v>2.097963126791748</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.911423570987947</v>
+        <v>-7.011386127635523</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1986057390990008</v>
+        <v>0.15862071643997</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.418510184391727</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.172403015161437</v>
+        <v>2.112425481172891</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.848194199219598</v>
+        <v>-6.948156755867175</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2184296082655353</v>
+        <v>0.1784445856065044</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.418510184391727</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.166935135620632</v>
+        <v>2.106957601632086</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.724903064402468</v>
+        <v>-6.824865621050044</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2652441562029644</v>
+        <v>0.2252591335439336</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.195256492927019</v>
+        <v>-1.295219049574597</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.238407910521488</v>
+        <v>2.178430376532941</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.703753865499024</v>
+        <v>-6.803716422146601</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2814048140016667</v>
+        <v>0.2414197913426364</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.174107294023576</v>
+        <v>-1.274069850671153</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.258798408100879</v>
+        <v>2.198820874112332</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.45998842351558</v>
+        <v>-6.559950980163157</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3746916991420952</v>
+        <v>0.3347066764830644</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.174107294023576</v>
+        <v>-1.274069850671153</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.254579116447929</v>
+        <v>2.194601582459383</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.313091395797709</v>
+        <v>-6.413053952445287</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4355748241492594</v>
+        <v>0.3955898014902286</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.126449052044988</v>
+        <v>-1.226411608692565</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.285298375555098</v>
+        <v>2.225320841566552</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.063241001848635</v>
+        <v>-6.163203558496212</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5282570567125915</v>
+        <v>0.4882720340535607</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.126449052044988</v>
+        <v>-1.226411608692565</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.2780404505388</v>
+        <v>2.218062916550254</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.887348909381203</v>
+        <v>-5.98731146602878</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6022130172202131</v>
+        <v>0.5622279945611823</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.126449052044988</v>
+        <v>-1.226411608692565</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.281639574059449</v>
+        <v>2.221662040070902</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.715902446358739</v>
+        <v>-5.815865003006317</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6841191084837521</v>
+        <v>0.6441340858247213</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9550025890225248</v>
+        <v>-1.054965145670102</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.39783495792748</v>
+        <v>2.337857423938934</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.490869446689916</v>
+        <v>-5.590832003337494</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7731527859675782</v>
+        <v>0.7331677633085474</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7299695893537019</v>
+        <v>-0.8299321460012795</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.531875235345071</v>
+        <v>2.471897701356525</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.427233704455982</v>
+        <v>-5.527196261103559</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8033018839154695</v>
+        <v>0.7633168612564383</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6663338471197674</v>
+        <v>-0.766296403767345</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.574751481739749</v>
+        <v>2.514773947751203</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.334233663250084</v>
+        <v>-5.434196219897661</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8216961591816245</v>
+        <v>0.7817111365225933</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6663338471197674</v>
+        <v>-0.766296403767345</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.555945740523545</v>
+        <v>2.495968206534998</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.093803166445223</v>
+        <v>-5.193765723092801</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9196114345284458</v>
+        <v>0.879626411869415</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4259033503149071</v>
+        <v>-0.5258659069624847</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.701947115231338</v>
+        <v>2.641969581242792</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.021560598274029</v>
+        <v>-5.121523154921606</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9524377756317439</v>
+        <v>0.9124527529727131</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4259033503149071</v>
+        <v>-0.5258659069624847</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.705876429066159</v>
+        <v>2.645898895077612</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.968562275992641</v>
+        <v>-5.068524832640218</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9743156884616391</v>
+        <v>0.9343306658026083</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3705670913129683</v>
+        <v>-0.4705296479605459</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.739756768384662</v>
+        <v>2.679779234396115</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.859757390512914</v>
+        <v>-4.959719947160491</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.014835713873523</v>
+        <v>0.9748506912144923</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3705670913129683</v>
+        <v>-0.4705296479605459</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.736754839604655</v>
+        <v>2.676777305616109</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.818665376145933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.639736592475903</v>
+        <v>-4.739699149123481</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.104423070098942</v>
+        <v>1.064438047439911</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.229347246244988</v>
+        <v>-0.3293098028925656</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.823065783656058</v>
+        <v>2.763088249667511</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.506868903412625</v>
+        <v>-4.606831460060203</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.173464328526076</v>
+        <v>1.133479305867045</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.229347246244988</v>
+        <v>-0.3293098028925656</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.838959966457881</v>
+        <v>2.778982432469335</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.347353799893256</v>
+        <v>-4.447316356540833</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.238416214374126</v>
+        <v>1.198431191715095</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06983214272561811</v>
+        <v>-0.1697946993731957</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.935814873009805</v>
+        <v>2.875837339021258</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.202681654793518</v>
+        <v>-4.302644211441096</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.306373174975461</v>
+        <v>1.26638815231643</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.07484000237411931</v>
+        <v>-0.02512255427345828</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.032706262631087</v>
+        <v>2.972728728642541</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.262556482151211</v>
+        <v>-4.362519038798788</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.26846073543381</v>
+        <v>1.228475712774779</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.01496517501642719</v>
+        <v>-0.08499738163115039</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.982818857617898</v>
+        <v>2.922841323629351</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.175756984372201</v>
+        <v>-4.404903940066755</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.325581027867979</v>
+        <v>1.233922245590158</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.01496517501642719</v>
+        <v>-0.08499738163115039</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.005219350940464</v>
+        <v>2.945241816951917</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.178226690834007</v>
+        <v>-4.407373646528561</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.324665546656669</v>
+        <v>1.233006764378848</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01249546855462103</v>
+        <v>-0.08746708809295656</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.003809928436792</v>
+        <v>2.943832394448246</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.246596877158018</v>
+        <v>-4.475743832852571</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.308324394601767</v>
+        <v>1.216665612323946</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.07819138905674161</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.020382270333223</v>
+        <v>2.960404736344677</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.355135058074151</v>
+        <v>-4.584282013768705</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.255345830867205</v>
+        <v>1.163687048589383</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.07819138905674161</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.010818978965114</v>
+        <v>2.950841444976568</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.386128217402857</v>
+        <v>-4.615275173097411</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.067658132176109</v>
+        <v>0.975999349898288</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.07819138905674161</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.835528544005501</v>
+        <v>2.775551010016955</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675893</v>
+        <v>3.746038950675895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.210653957610388</v>
+        <v>-4.439800913304941</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.142415068084885</v>
+        <v>1.050756285807064</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.07819138905674161</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.840095775997289</v>
+        <v>2.780118242008743</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695438</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.321590210251637</v>
+        <v>-4.55073716594619</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.073782595789592</v>
+        <v>0.9821238135117711</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.07819138905674161</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.815837804758496</v>
+        <v>2.75586027076995</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.52461678779487</v>
+        <v>-4.753763743489423</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9957033499922046</v>
+        <v>0.9040445677143834</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1812554099523974</v>
+        <v>-0.281217966599975</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.697153243452462</v>
+        <v>2.637175709463915</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.366691188859577</v>
+        <v>-4.59583814455413</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.069045975998454</v>
+        <v>0.9773871937206329</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1812554099523974</v>
+        <v>-0.281217966599975</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.707325629884594</v>
+        <v>2.647348095896048</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.280447725833199</v>
+        <v>-4.509594681527752</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.098489631782865</v>
+        <v>1.006830849505044</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1812554099523974</v>
+        <v>-0.281217966599975</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.702271900458455</v>
+        <v>2.642294366469908</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786042</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.281630810484261</v>
+        <v>-4.510777766178814</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.089792173366966</v>
+        <v>0.9981333910891452</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.186898458418909</v>
+        <v>-0.2868610150664865</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.690661846823073</v>
+        <v>2.630684312834526</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273188</v>
+        <v>3.75356759027319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.158503103490178</v>
+        <v>-4.387650059184731</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.139595129197701</v>
+        <v>1.04793634691988</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.186898458418909</v>
+        <v>-0.2868610150664865</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.691213719856175</v>
+        <v>2.631236185867628</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279497</v>
+        <v>3.733387025279499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.184901365251918</v>
+        <v>-4.294839577733871</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.058308516384371</v>
+        <v>1.01433323139159</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2132967201806493</v>
+        <v>-0.1940505336156272</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.604647454690496</v>
+        <v>2.616195166629509</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.136338313030889</v>
+        <v>-4.246276525512841</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.079607213197384</v>
+        <v>1.035631928204602</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1647336679596191</v>
+        <v>-0.145487481394597</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.635658761947715</v>
+        <v>2.647206473886728</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.023667094794638</v>
+        <v>-4.133605307276591</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.119751409003606</v>
+        <v>1.075776124010825</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05206244972336888</v>
+        <v>-0.03281626315834679</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.698337201401188</v>
+        <v>2.709884913340201</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.911290093611966</v>
+        <v>-4.021228306093918</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.170193505307343</v>
+        <v>1.126218220314562</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05206244972336888</v>
+        <v>-0.03281626315834679</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.703828497231855</v>
+        <v>2.715376209170869</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.109524662498696</v>
+        <v>-4.219462874980649</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.10239687952119</v>
+        <v>1.058421594528409</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2502970186100995</v>
+        <v>-0.2310508320450774</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.596384957668356</v>
+        <v>2.607932669607369</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175319</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.192525943523975</v>
+        <v>-4.302464156005928</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9075520871117313</v>
+        <v>0.8635768021189503</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2688679031372732</v>
+        <v>-0.2496217165722511</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.423598146952705</v>
+        <v>2.435145858891718</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199264</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.319592949830963</v>
+        <v>-4.429531162312916</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9768749453081418</v>
+        <v>0.9328996603153608</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2688679031372732</v>
+        <v>-0.2496217165722511</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.543747807671911</v>
+        <v>2.555295519610924</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.733008865660764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.406191532812066</v>
+        <v>-4.516129745294019</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9567485382180236</v>
+        <v>0.9127732532252426</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2688679031372732</v>
+        <v>-0.2496217165722511</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.558260833774234</v>
+        <v>2.569808545713247</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383418</v>
+        <v>3.74117049438342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.367807870253915</v>
+        <v>-4.477746082735868</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9695214445836526</v>
+        <v>0.9255461595908716</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.230484240579122</v>
+        <v>-0.2112380540141</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.578710472651493</v>
+        <v>2.590258184590506</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002479</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.190691540218749</v>
+        <v>-4.300629752700702</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.037097005443021</v>
+        <v>0.9931217204502401</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.230484240579122</v>
+        <v>-0.2112380540141</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.575439501496795</v>
+        <v>2.586987213435808</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263896</v>
+        <v>3.741324873263897</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160989416242455</v>
+        <v>-4.270927628724408</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.049661246795452</v>
+        <v>1.005685961802671</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2349543657944354</v>
+        <v>-0.2157081792294133</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.57344081812952</v>
+        <v>2.584988530068533</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481228</v>
+        <v>3.75072580148123</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981613995003688</v>
+        <v>-4.09155220748564</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.115198390597373</v>
+        <v>1.071223105604592</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07817760762371673</v>
+        <v>-0.05893142105869464</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.661293848338365</v>
+        <v>2.672841560277379</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452223</v>
+        <v>3.716988143452225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026628208524293</v>
+        <v>-4.136566421006247</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.078000160520721</v>
+        <v>1.034024875527939</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1085265029383213</v>
+        <v>-0.08928031637329925</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.623891966481192</v>
+        <v>2.635439678420206</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293632718796728</v>
+        <v>-4.403570931278682</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9768899187506923</v>
+        <v>0.9329146337579108</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3028895409812699</v>
+        <v>-0.2836433544162478</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.512965705994369</v>
+        <v>2.524513417933382</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.582419939255644</v>
+        <v>-4.692358151737597</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8605789524636276</v>
+        <v>0.8166036674708461</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4039756610802703</v>
+        <v>-0.3847294745152482</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.45151795583147</v>
+        <v>2.463065667770484</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.549944353084872</v>
+        <v>-4.659882565566825</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8711691484862532</v>
+        <v>0.8271938634934717</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4039756610802703</v>
+        <v>-0.3847294745152482</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.449117917385787</v>
+        <v>2.4606656293248</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.530906225377574</v>
+        <v>-4.640844437859528</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8753091187774169</v>
+        <v>0.8313338337846357</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4621592724114648</v>
+        <v>-0.4429130858464427</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.410732469795315</v>
+        <v>2.422280181734329</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.562032856528193</v>
+        <v>-4.671971069010146</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.04044033525585</v>
+        <v>0.9964650502630688</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4621592724114648</v>
+        <v>-0.4429130858464427</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.588314338733996</v>
+        <v>2.599862050673009</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.614353237128984</v>
+        <v>-4.724291449610938</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.020345512001667</v>
+        <v>0.9763702270088856</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4272124124025927</v>
+        <v>-0.4079662258375706</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.610115783725453</v>
+        <v>2.621663495664466</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259118</v>
+        <v>3.78742200525912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.758676143053903</v>
+        <v>-4.868614355535857</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9686248800286255</v>
+        <v>0.924649595035844</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4272124124025927</v>
+        <v>-0.4079662258375706</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.616124314122379</v>
+        <v>2.627672026061392</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989903</v>
+        <v>3.781497674989905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.610933172818901</v>
+        <v>-4.720871385300854</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.106874715914648</v>
+        <v>1.062899430921867</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2594050551677095</v>
+        <v>-0.2401588686026874</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795961376255331</v>
+        <v>2.807509088194344</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651165</v>
+        <v>3.802242353651167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.712947855350122</v>
+        <v>-4.822886067832076</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.068862464433641</v>
+        <v>1.024887179440859</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2594050551677095</v>
+        <v>-0.2401588686026874</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.798754997786812</v>
+        <v>2.810302709725825</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864723</v>
+        <v>3.805605409864725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.576338511256029</v>
+        <v>-4.686276723737983</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.124168550462936</v>
+        <v>1.080193265470155</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.122795711073617</v>
+        <v>-0.1035495245085949</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.881382952634925</v>
+        <v>2.892930664573939</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360613</v>
+        <v>3.798236219360614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.719103844078679</v>
+        <v>-4.829042056560633</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.066142894073987</v>
+        <v>1.022167609081205</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2655610438962674</v>
+        <v>-0.2463148573312454</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.794804229681445</v>
+        <v>2.806351941620459</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268422</v>
+        <v>3.867359061268424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.656805845302557</v>
+        <v>-4.766744057784511</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.157397647381256</v>
+        <v>1.113422362388475</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2655610438962674</v>
+        <v>-0.2463148573312454</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861139783478266</v>
+        <v>2.87268749541728</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462185</v>
+        <v>3.848725564462187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.455015647637399</v>
+        <v>-4.564953860119353</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9466945988367175</v>
+        <v>0.902719313843936</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.06754285172711305</v>
+        <v>-0.04829666516209097</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.688531571169157</v>
+        <v>2.70007928310817</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144124232242</v>
+        <v>3.841441242322421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.395124965994806</v>
+        <v>-4.505063178476759</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.04094110381593</v>
+        <v>0.9969658188231487</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.007652170084519572</v>
+        <v>0.01159401648050251</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794756212476888</v>
+        <v>2.806303924415901</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.517519711190525</v>
+        <v>3.572139161602025</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.49286551061978</v>
+        <v>-4.602803723101734</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.016472622081984</v>
+        <v>0.9724973370892025</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02354144821749976</v>
+        <v>-0.004295261652477678</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799850381713143</v>
+        <v>2.811398093652157</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-51.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-681.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.9%</t>
+          <t>441.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-621.9%</t>
+          <t>-635.5%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,16 +1131,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-273.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.0%</t>
+          <t>-284.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-99.9%</t>
+          <t>-282.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.4%</t>
+          <t>-214.4%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.9%</t>
+          <t>-186.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1973"/>
+  <dimension ref="A1:G1974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706676</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296843</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.808334002926732</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.797638736842286</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201493</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-1.015899787318344</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.712437219204881</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153012</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.433653810865181</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.54326250129121</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537431</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.473824781011824</v>
+        <v>-1.636943280186983</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.527060329831475</v>
+        <v>2.461812930161411</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382196</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.681828839364901</v>
+        <v>-1.844947338540061</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448750851044169</v>
+        <v>2.383503451374105</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-2.056359759428036</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.294019939356903</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.395518137016558</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.151440887627943</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.604008918468242</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.088382864786038</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688091604058305</v>
+        <v>-2.851210103233464</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062848540958581</v>
+        <v>1.997601141288518</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180476632082402</v>
+        <v>-3.34359513125756</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.867000921792675</v>
+        <v>1.801753522122611</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.728775522187633</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.646223904563445</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-4.072458295414296</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.510519918727397</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-4.278970072301317</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.424021266628846</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.53481115808001</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.323457759017628</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.966616951229797</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.137068329225118</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-5.20131094536235</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.031475506574187</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.536973592592802</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.8957910393379716</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.900599837493115</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.7568281016120877</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.265727220131862</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.6100316635624203</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.67431599731254</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.4453576967049084</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.950892097628373</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.3299126890500359</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.36728397191537</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.1613499899441142</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.520777415280859</v>
+        <v>-7.683895914456018</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1102113032665977</v>
+        <v>0.04496390359653413</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.866652237265669</v>
+        <v>-8.029770736440828</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03203906038163096</v>
+        <v>-0.0972864600516945</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.030232115450053</v>
+        <v>-8.193350614625212</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09906609160038382</v>
+        <v>-0.1643134912704474</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.326893457260251</v>
+        <v>-8.49001195643541</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2139516523952549</v>
+        <v>-0.2791990520653185</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.45013784647568</v>
+        <v>-8.613256345650839</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2672757126158296</v>
+        <v>-0.3325231122858932</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.833139235218312</v>
+        <v>-8.99625773439347</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.420578369434466</v>
+        <v>-0.4858257691045296</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.990538115431432</v>
+        <v>-9.153656614606591</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4809664055482843</v>
+        <v>-0.5462138052183478</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.350068437935434</v>
+        <v>-9.513186937110593</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6194282312518347</v>
+        <v>-0.6846756309218982</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.400417501389656</v>
+        <v>-9.563536000564815</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6316518366763462</v>
+        <v>-0.6968992363464097</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776674</v>
+        <v>3.500446096776673</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.498036778811052</v>
+        <v>-9.661155277986211</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6676577970231357</v>
+        <v>-0.7329051966931992</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.494345853854641</v>
+        <v>-9.6574643530298</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6661814270405713</v>
+        <v>-0.7314288267106348</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.698604029184505</v>
+        <v>-9.861722528359664</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7423715000538746</v>
+        <v>-0.8076188997239382</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.840413803391293</v>
+        <v>-10.00353230256645</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7946128552521539</v>
+        <v>-0.8598602549222174</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.161965059483127</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.766943971723844</v>
+        <v>-9.930062470899003</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7498532210917528</v>
+        <v>-0.8151006207618163</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.088495227815679</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.942068389110387</v>
+        <v>-10.10518688828555</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8053477672988536</v>
+        <v>-0.8705951669689167</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.263619645202223</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.17652048312488</v>
+        <v>-10.33963898230004</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9063477698062452</v>
+        <v>-0.9715951694763088</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.263619645202223</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234399</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.46432432766212</v>
+        <v>-10.62744282683727</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.028141498395117</v>
+        <v>-1.093388898065181</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.551423489739461</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860589</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.51711048326244</v>
+        <v>-10.6802289824376</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.048140170796692</v>
+        <v>-1.113387570466755</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.647098976321858</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767403</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.7491394029987</v>
+        <v>-10.91225790217386</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.138258010062082</v>
+        <v>-1.203505409732145</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.709111673510281</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792547</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.69712388902989</v>
+        <v>-10.86024238820505</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.113461468788155</v>
+        <v>-1.178708868458219</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.709111673510281</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628925</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.83879573075401</v>
+        <v>-11.00191422992917</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.171605432376545</v>
+        <v>-1.236852832046608</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.709111673510281</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.78920488632918</v>
+        <v>-10.95232338550434</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.136715684441739</v>
+        <v>-1.201963084111803</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.659520829085447</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.59005277909208</v>
+        <v>-10.75317127826724</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.070105975193582</v>
+        <v>-1.135353374863646</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.494198303135634</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.36420762637267</v>
+        <v>-10.52732612554783</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9701888410696102</v>
+        <v>-1.035436240739674</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.45227162754847</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.23962897003508</v>
+        <v>-10.40274746921023</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9192182339785142</v>
+        <v>-0.9844656336485778</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.45227162754847</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.29252425807936</v>
+        <v>-10.45564275725452</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9377425750341208</v>
+        <v>-1.002989974704184</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.447316281460024</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.00861552715061</v>
+        <v>-10.17173402632577</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8184453784239851</v>
+        <v>-0.8836927780940487</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.447316281460024</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.937249134540966</v>
+        <v>-10.10036763371613</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7996360837739913</v>
+        <v>-0.8648834834440553</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.375949888850376</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.673412267336897</v>
+        <v>-9.836530766512055</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7039848182052713</v>
+        <v>-0.7692322178753348</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.375949888850376</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.406170466468499</v>
+        <v>-9.569288965643658</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5989226583572855</v>
+        <v>-0.6641700580273491</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.375949888850376</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.308263427792008</v>
+        <v>-9.471381926967167</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5600601578601503</v>
+        <v>-0.6253075575302138</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.30796413898982</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.28430988681605</v>
+        <v>-9.447428385991209</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5498102353242733</v>
+        <v>-0.6150576349943369</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.284010598013862</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487767</v>
+        <v>3.789307536487765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.020249948493253</v>
+        <v>-9.183368447668412</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4574465761569071</v>
+        <v>-0.5226939758269706</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.019950659691066</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.313170324988416</v>
+        <v>-8.476288824163575</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1774017604152727</v>
+        <v>-0.2426491600853362</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.019950659691066</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858723</v>
+        <v>3.839370871858721</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.272986026622226</v>
+        <v>-8.436104525797385</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1609844171809551</v>
+        <v>-0.2262318168510187</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.979766361324875</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096468</v>
+        <v>3.856158176096466</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.192916231084421</v>
+        <v>-8.35603473025958</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1295896777450767</v>
+        <v>-0.1948370774151402</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.899696565787071</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.959435008854823</v>
+        <v>-8.122553508029981</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.0282727600153847</v>
+        <v>-0.0935201596854478</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.666215343557473</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.809768617847308</v>
+        <v>-7.972887117022466</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.028701586074662</v>
+        <v>-0.0365458135954011</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.573311852314937</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.677493144216421</v>
+        <v>-7.840611643391579</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.0769792622740435</v>
+        <v>0.0117318626039804</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.44103637868405</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.586856026190845</v>
+        <v>-7.650011968718426</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1160491701719106</v>
+        <v>0.09078679316087834</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.350399260658475</v>
+        <v>-1.250436704010897</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.340908448566912</v>
+        <v>2.400885982555458</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.337856227507264</v>
+        <v>-7.401012170034845</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2285554308690019</v>
+        <v>0.2032930538579696</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.350399260658475</v>
+        <v>-1.250436704010897</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.353814789790571</v>
+        <v>2.413792323779117</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.443446217280369</v>
+        <v>-7.50660215980795</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.05834350536054167</v>
+        <v>0.03308112834950894</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.455989250431579</v>
+        <v>-1.356026693784002</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.162484866327489</v>
+        <v>2.222462400316036</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.462181119398966</v>
+        <v>-7.525337061926547</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.09939388639018887</v>
+        <v>0.07413150937915658</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.455989250431579</v>
+        <v>-1.356026693784002</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.211029208204575</v>
+        <v>2.271006742193122</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.314241077991366</v>
+        <v>-7.377397020518948</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.03869098026506101</v>
+        <v>0.01342860325402873</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.435668334523021</v>
+        <v>-1.335705777875444</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.103342835061543</v>
+        <v>2.163320369050089</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.297082927860072</v>
+        <v>-7.360238870387653</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.03684025406410063</v>
+        <v>0.01157787705306834</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.418510184391727</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.104923738886841</v>
+        <v>2.164901272875387</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.253534521089382</v>
+        <v>-7.316690463616963</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.04729900467728365</v>
+        <v>0.02203662766625136</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.418510184391727</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.097963126791748</v>
+        <v>2.157940660780294</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.011386127635523</v>
+        <v>-7.074542070163105</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.15862071643997</v>
+        <v>0.1333583394289377</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.418510184391727</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.112425481172891</v>
+        <v>2.172403015161437</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.948156755867175</v>
+        <v>-7.011312698394756</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1784445856065044</v>
+        <v>0.1531822085954717</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.418510184391727</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.106957601632086</v>
+        <v>2.166935135620632</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.824865621050044</v>
+        <v>-6.888021563577626</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2252591335439336</v>
+        <v>0.1999967565329013</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.295219049574597</v>
+        <v>-1.195256492927019</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.178430376532941</v>
+        <v>2.238407910521488</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389912</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.803716422146601</v>
+        <v>-6.866872364674182</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2414197913426364</v>
+        <v>0.2161574143316036</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.274069850671153</v>
+        <v>-1.174107294023576</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.198820874112332</v>
+        <v>2.258798408100879</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.559950980163157</v>
+        <v>-6.623106922690738</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3347066764830644</v>
+        <v>0.3094442994720321</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.274069850671153</v>
+        <v>-1.174107294023576</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.194601582459383</v>
+        <v>2.254579116447929</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.413053952445287</v>
+        <v>-6.476209894972868</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3955898014902286</v>
+        <v>0.3703274244791959</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.226411608692565</v>
+        <v>-1.126449052044988</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.225320841566552</v>
+        <v>2.285298375555098</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.163203558496212</v>
+        <v>-6.226359501023794</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4882720340535607</v>
+        <v>0.4630096570425279</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.226411608692565</v>
+        <v>-1.126449052044988</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.218062916550254</v>
+        <v>2.2780404505388</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.98731146602878</v>
+        <v>-6.050467408556361</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5622279945611823</v>
+        <v>0.5369656175501496</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.226411608692565</v>
+        <v>-1.126449052044988</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.221662040070902</v>
+        <v>2.281639574059449</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.815865003006317</v>
+        <v>-5.879020945533898</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6441340858247213</v>
+        <v>0.6188717088136886</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.054965145670102</v>
+        <v>-0.9550025890225248</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.337857423938934</v>
+        <v>2.39783495792748</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.590832003337494</v>
+        <v>-5.653987945865075</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7331677633085474</v>
+        <v>0.7079053862975146</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8299321460012795</v>
+        <v>-0.7299695893537019</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.471897701356525</v>
+        <v>2.531875235345071</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.527196261103559</v>
+        <v>-5.590352203631141</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7633168612564383</v>
+        <v>0.738054484245406</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.766296403767345</v>
+        <v>-0.6663338471197674</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.514773947751203</v>
+        <v>2.574751481739749</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.434196219897661</v>
+        <v>-5.497352162425242</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7817111365225933</v>
+        <v>0.756448759511561</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.766296403767345</v>
+        <v>-0.6663338471197674</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.495968206534998</v>
+        <v>2.555945740523545</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.193765723092801</v>
+        <v>-5.256921665620382</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.879626411869415</v>
+        <v>0.8543640348583823</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5258659069624847</v>
+        <v>-0.4259033503149071</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.641969581242792</v>
+        <v>2.701947115231338</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.121523154921606</v>
+        <v>-5.184679097449187</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9124527529727131</v>
+        <v>0.8871903759616804</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5258659069624847</v>
+        <v>-0.4259033503149071</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.645898895077612</v>
+        <v>2.705876429066159</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.068524832640218</v>
+        <v>-5.1316807751678</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9343306658026083</v>
+        <v>0.9090682887915755</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4705296479605459</v>
+        <v>-0.3705670913129683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.679779234396115</v>
+        <v>2.739756768384662</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972334</v>
+        <v>3.848613050972332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.959719947160491</v>
+        <v>-5.022875889688073</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9748506912144923</v>
+        <v>0.94958831420346</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4705296479605459</v>
+        <v>-0.3705670913129683</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.676777305616109</v>
+        <v>2.736754839604655</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145933</v>
+        <v>3.818665376145931</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.739699149123481</v>
+        <v>-4.802855091651062</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.064438047439911</v>
+        <v>1.039175670428878</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3293098028925656</v>
+        <v>-0.229347246244988</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.763088249667511</v>
+        <v>2.823065783656058</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.606831460060203</v>
+        <v>-4.669987402587784</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.133479305867045</v>
+        <v>1.108216928856013</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3293098028925656</v>
+        <v>-0.229347246244988</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.778982432469335</v>
+        <v>2.838959966457881</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.447316356540833</v>
+        <v>-4.510472299068415</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.198431191715095</v>
+        <v>1.173168814704062</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1697946993731957</v>
+        <v>-0.06983214272561811</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.875837339021258</v>
+        <v>2.935814873009805</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.302644211441096</v>
+        <v>-4.365800153968677</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.26638815231643</v>
+        <v>1.241125775305397</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02512255427345828</v>
+        <v>0.07484000237411931</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.972728728642541</v>
+        <v>3.032706262631087</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412105</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.362519038798788</v>
+        <v>-4.425674981326369</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.228475712774779</v>
+        <v>1.203213335763746</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08499738163115039</v>
+        <v>0.01496517501642719</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.922841323629351</v>
+        <v>2.982818857617898</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144518</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.404903940066755</v>
+        <v>-4.33887548354736</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.233922245590158</v>
+        <v>1.260333628197916</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08499738163115039</v>
+        <v>0.01496517501642719</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.945241816951917</v>
+        <v>3.005219350940464</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.407373646528561</v>
+        <v>-4.341345190009166</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.233006764378848</v>
+        <v>1.259418146986606</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08746708809295656</v>
+        <v>0.01249546855462103</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.943832394448246</v>
+        <v>3.003809928436792</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.475743832852571</v>
+        <v>-4.409715376333176</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.216665612323946</v>
+        <v>1.243076994931704</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.07819138905674161</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.960404736344677</v>
+        <v>3.020382270333223</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.584282013768705</v>
+        <v>-4.51825355724931</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.163687048589383</v>
+        <v>1.190098431197141</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.07819138905674161</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.950841444976568</v>
+        <v>3.010818978965114</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.615275173097411</v>
+        <v>-4.549246716578016</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.975999349898288</v>
+        <v>1.002410732506046</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.07819138905674161</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.775551010016955</v>
+        <v>2.835528544005501</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675895</v>
+        <v>3.746038950675892</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.439800913304941</v>
+        <v>-4.373772456785547</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.050756285807064</v>
+        <v>1.077167668414821</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.07819138905674161</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.780118242008743</v>
+        <v>2.840095775997289</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.55073716594619</v>
+        <v>-4.484708709426796</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9821238135117711</v>
+        <v>1.008535196119529</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.07819138905674161</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.75586027076995</v>
+        <v>2.815837804758496</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.753763743489423</v>
+        <v>-4.687735286970029</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9040445677143834</v>
+        <v>0.930455950322141</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.281217966599975</v>
+        <v>-0.1812554099523974</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.637175709463915</v>
+        <v>2.697153243452462</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.59583814455413</v>
+        <v>-4.529809688034736</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9773871937206329</v>
+        <v>1.003798576328391</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.281217966599975</v>
+        <v>-0.1812554099523974</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.647348095896048</v>
+        <v>2.707325629884594</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.509594681527752</v>
+        <v>-4.443566225008358</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.006830849505044</v>
+        <v>1.033242232112802</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.281217966599975</v>
+        <v>-0.1812554099523974</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.642294366469908</v>
+        <v>2.702271900458455</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.510777766178814</v>
+        <v>-4.44474930965942</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9981333910891452</v>
+        <v>1.024544773696903</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2868610150664865</v>
+        <v>-0.186898458418909</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.630684312834526</v>
+        <v>2.690661846823073</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75356759027319</v>
+        <v>3.753567590273188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.387650059184731</v>
+        <v>-4.321621602665337</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.04793634691988</v>
+        <v>1.074347729527638</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2868610150664865</v>
+        <v>-0.186898458418909</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.631236185867628</v>
+        <v>2.691213719856175</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279499</v>
+        <v>3.733387025279497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.294839577733871</v>
+        <v>-4.228811121214477</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.01433323139159</v>
+        <v>1.040744613999347</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1940505336156272</v>
+        <v>-0.0940879769680496</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.616195166629509</v>
+        <v>2.676172700618056</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.246276525512841</v>
+        <v>-4.180248068993447</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.035631928204602</v>
+        <v>1.06204331081236</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.145487481394597</v>
+        <v>-0.04552492474701941</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.647206473886728</v>
+        <v>2.707184007875275</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.133605307276591</v>
+        <v>-4.067576850757197</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.075776124010825</v>
+        <v>1.102187506618583</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03281626315834679</v>
+        <v>0.06714629348923079</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.709884913340201</v>
+        <v>2.769862447328748</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.021228306093918</v>
+        <v>-4.116933623869789</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.126218220314562</v>
+        <v>1.087936093204213</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03281626315834679</v>
+        <v>0.06714629348923079</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.715376209170869</v>
+        <v>2.775353743159415</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.219462874980649</v>
+        <v>-4.31516819275652</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.058421594528409</v>
+        <v>1.02013946741806</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2310508320450774</v>
+        <v>-0.1310882753974998</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.607932669607369</v>
+        <v>2.667910203595916</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.302464156005928</v>
+        <v>-4.398169473781799</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8635768021189503</v>
+        <v>0.8252946750086019</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2496217165722511</v>
+        <v>-0.1496591599246735</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.435145858891718</v>
+        <v>2.495123392880265</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199265</v>
+        <v>3.682712735199264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.429531162312916</v>
+        <v>-4.525236480088787</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9328996603153608</v>
+        <v>0.8946175332050124</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2496217165722511</v>
+        <v>-0.1496591599246735</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.555295519610924</v>
+        <v>2.61527305359947</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660764</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.516129745294019</v>
+        <v>-4.61183506306989</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9127732532252426</v>
+        <v>0.874491126114894</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2496217165722511</v>
+        <v>-0.1496591599246735</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.569808545713247</v>
+        <v>2.629786079701793</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117049438342</v>
+        <v>3.741170494383418</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.477746082735868</v>
+        <v>-4.573451400511739</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9255461595908716</v>
+        <v>0.8872640324805232</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2112380540141</v>
+        <v>-0.1112754973665224</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.590258184590506</v>
+        <v>2.650235718579053</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002479</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.300629752700702</v>
+        <v>-4.396335070476573</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9931217204502401</v>
+        <v>0.9548395933398917</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2112380540141</v>
+        <v>-0.1112754973665224</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.586987213435808</v>
+        <v>2.646964747424355</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263897</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.270927628724408</v>
+        <v>-4.366632946500279</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.005685961802671</v>
+        <v>0.9674038346923222</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2157081792294133</v>
+        <v>-0.1157456225818357</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.584988530068533</v>
+        <v>2.64496606405708</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072580148123</v>
+        <v>3.750725801481228</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.09155220748564</v>
+        <v>-4.187257525261511</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.071223105604592</v>
+        <v>1.032940978494244</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05893142105869464</v>
+        <v>0.04103113558888294</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.672841560277379</v>
+        <v>2.732819094265925</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452225</v>
+        <v>3.716988143452223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.136566421006247</v>
+        <v>-4.232271738782117</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.034024875527939</v>
+        <v>0.9957427484175909</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08928031637329925</v>
+        <v>0.01068224027427833</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.635439678420206</v>
+        <v>2.695417212408752</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979531</v>
+        <v>3.737023032979529</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.403570931278682</v>
+        <v>-4.499276249054552</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9329146337579108</v>
+        <v>0.8946325066475627</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2836433544162478</v>
+        <v>-0.1836807977686702</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.524513417933382</v>
+        <v>2.584490951921929</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.692358151737597</v>
+        <v>-4.788063469513467</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8166036674708461</v>
+        <v>0.7783215403604982</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3847294745152482</v>
+        <v>-0.2847669178676706</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.463065667770484</v>
+        <v>2.52304320175903</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.659882565566825</v>
+        <v>-4.755587883342695</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8271938634934717</v>
+        <v>0.7889117363831237</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3847294745152482</v>
+        <v>-0.2847669178676706</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.4606656293248</v>
+        <v>2.520643163313347</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.640844437859528</v>
+        <v>-4.736549755635398</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8313338337846357</v>
+        <v>0.7930517066742875</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4429130858464427</v>
+        <v>-0.3429505291988652</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.422280181734329</v>
+        <v>2.482257715722875</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.671971069010146</v>
+        <v>-4.767676386786016</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9964650502630688</v>
+        <v>0.9581829231527208</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4429130858464427</v>
+        <v>-0.3429505291988652</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.599862050673009</v>
+        <v>2.659839584661556</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537864</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.724291449610938</v>
+        <v>-4.819996767386808</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9763702270088856</v>
+        <v>0.9380880998985375</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4079662258375706</v>
+        <v>-0.308003669189993</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.621663495664466</v>
+        <v>2.681641029653012</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742200525912</v>
+        <v>3.787422005259118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.868614355535857</v>
+        <v>-4.964319673311727</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.924649595035844</v>
+        <v>0.886367467925496</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4079662258375706</v>
+        <v>-0.308003669189993</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.627672026061392</v>
+        <v>2.687649560049938</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989905</v>
+        <v>3.781497674989903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.720871385300854</v>
+        <v>-4.816576703076724</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.062899430921867</v>
+        <v>1.024617303811519</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2401588686026874</v>
+        <v>-0.1401963119551098</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.807509088194344</v>
+        <v>2.86748662218289</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651167</v>
+        <v>3.802242353651165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.822886067832076</v>
+        <v>-4.918591385607946</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.024887179440859</v>
+        <v>0.9866050523305114</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2401588686026874</v>
+        <v>-0.1401963119551098</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.810302709725825</v>
+        <v>2.870280243714371</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864725</v>
+        <v>3.805605409864723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.686276723737983</v>
+        <v>-4.781982041513853</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.080193265470155</v>
+        <v>1.041911138359807</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1035495245085949</v>
+        <v>-0.003586967861017365</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.892930664573939</v>
+        <v>2.952908198562485</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360614</v>
+        <v>3.798236219360611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.829042056560633</v>
+        <v>-4.924747374336503</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.022167609081205</v>
+        <v>0.9838854819708569</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2463148573312454</v>
+        <v>-0.1463523006836678</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.806351941620459</v>
+        <v>2.866329475609005</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268424</v>
+        <v>3.867359061268422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.766744057784511</v>
+        <v>-4.903634401948034</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.113422362388475</v>
+        <v>1.058666224723065</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2463148573312454</v>
+        <v>-0.1463523006836678</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.87268749541728</v>
+        <v>2.932665029405826</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462187</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.564953860119353</v>
+        <v>-4.701844204282876</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.902719313843936</v>
+        <v>0.8479631761785267</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.04829666516209097</v>
+        <v>0.05166589148548661</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.70007928310817</v>
+        <v>2.760056817096717</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322421</v>
+        <v>3.84144124232242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.505063178476759</v>
+        <v>-4.641953522640283</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9969658188231487</v>
+        <v>0.9422096811577392</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.01159401648050251</v>
+        <v>0.1115565731280801</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.806303924415901</v>
+        <v>2.866281458404448</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,45 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.572139161602025</v>
+        <v>3.819059724789552</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.602803723101734</v>
+        <v>-4.739694067265257</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9724973370892025</v>
+        <v>0.917741199423793</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.004295261652477678</v>
+        <v>0.09566729499509991</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.811398093652157</v>
+        <v>2.871375627640703</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="2" t="n">
+        <v>45436</v>
+      </c>
+      <c r="B1974" t="n">
+        <v>3.449122134360777</v>
+      </c>
+      <c r="C1974" t="n">
+        <v>2.60141803624519</v>
+      </c>
+      <c r="D1974" t="n">
+        <v>-4.739694067265257</v>
+      </c>
+      <c r="E1974" t="n">
+        <v>0.917741199423793</v>
+      </c>
+      <c r="F1974" t="n">
+        <v>0.09566729499509991</v>
+      </c>
+      <c r="G1974" t="n">
+        <v>2.594481833231558</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.7%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.2%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-635.5%</t>
+          <t>-589.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.1%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.4%</t>
+          <t>-265.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>199.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-282.1%</t>
+          <t>-284.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-214.4%</t>
+          <t>-210.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.6%</t>
+          <t>-160.9%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.808334002926732</v>
+        <v>-0.6452155037515721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.797638736842286</v>
+        <v>2.86288613651235</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.015899787318344</v>
+        <v>-0.852781288143184</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.712437219204881</v>
+        <v>2.777684618874945</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.433653810865181</v>
+        <v>-1.270535311690021</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.54326250129121</v>
+        <v>2.608509900961274</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.636943280186983</v>
+        <v>-1.473824781011824</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.461812930161411</v>
+        <v>2.527060329831475</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.844947338540061</v>
+        <v>-1.681828839364901</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.383503451374105</v>
+        <v>2.448750851044169</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.056359759428036</v>
+        <v>-1.893241260252876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.294019939356903</v>
+        <v>2.359267339026967</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.395518137016558</v>
+        <v>-2.232399637841398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.151440887627943</v>
+        <v>2.216688287298007</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.604008918468242</v>
+        <v>-2.440890419293083</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.088382864786038</v>
+        <v>2.153630264456102</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.851210103233464</v>
+        <v>-2.688091604058305</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.997601141288518</v>
+        <v>2.062848540958581</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.34359513125756</v>
+        <v>-3.180476632082402</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.801753522122611</v>
+        <v>1.867000921792675</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.728775522187633</v>
+        <v>-3.565657023012474</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.646223904563445</v>
+        <v>1.711471304233509</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.072458295414296</v>
+        <v>-3.909339796239137</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.510519918727397</v>
+        <v>1.57576731839746</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.278970072301317</v>
+        <v>-4.115851573126158</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.424021266628846</v>
+        <v>1.489268666298909</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.53481115808001</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.323457759017628</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.966616951229797</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.137068329225118</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.20131094536235</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.031475506574187</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.536973592592802</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8957910393379716</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.900599837493115</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7568281016120877</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.265727220131862</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6100316635624203</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.67431599731254</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4453576967049084</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.950892097628373</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3299126890500359</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.36728397191537</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1613499899441142</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.683895914456018</v>
+        <v>-7.520777415280859</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04496390359653413</v>
+        <v>0.1102113032665977</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.029770736440828</v>
+        <v>-7.866652237265669</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0972864600516945</v>
+        <v>-0.03203906038163096</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.193350614625212</v>
+        <v>-8.030232115450053</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1643134912704474</v>
+        <v>-0.09906609160038382</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.49001195643541</v>
+        <v>-8.326893457260251</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2791990520653185</v>
+        <v>-0.2139516523952549</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.613256345650839</v>
+        <v>-8.45013784647568</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3325231122858932</v>
+        <v>-0.2672757126158296</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.99625773439347</v>
+        <v>-8.833139235218312</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4858257691045296</v>
+        <v>-0.420578369434466</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.153656614606591</v>
+        <v>-8.990538115431432</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5462138052183478</v>
+        <v>-0.4809664055482843</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.513186937110593</v>
+        <v>-9.350068437935434</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6846756309218982</v>
+        <v>-0.6194282312518347</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.563536000564815</v>
+        <v>-9.400417501389656</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6968992363464097</v>
+        <v>-0.6316518366763462</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776673</v>
+        <v>3.500446096776672</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.661155277986211</v>
+        <v>-9.498036778811052</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7329051966931992</v>
+        <v>-0.6676577970231357</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.6574643530298</v>
+        <v>-9.494345853854641</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7314288267106348</v>
+        <v>-0.6661814270405713</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.861722528359664</v>
+        <v>-9.698604029184505</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8076188997239382</v>
+        <v>-0.7423715000538746</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.00353230256645</v>
+        <v>-9.840413803391293</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8598602549222174</v>
+        <v>-0.7946128552521539</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.161965059483127</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.930062470899003</v>
+        <v>-9.766943971723844</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8151006207618163</v>
+        <v>-0.7498532210917528</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.088495227815679</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.10518688828555</v>
+        <v>-9.942068389110387</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8705951669689167</v>
+        <v>-0.8053477672988536</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.263619645202223</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.33963898230004</v>
+        <v>-10.17652048312488</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9715951694763088</v>
+        <v>-0.9063477698062452</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.263619645202223</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.62744282683727</v>
+        <v>-10.46432432766212</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.093388898065181</v>
+        <v>-1.028141498395117</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.551423489739461</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.6802289824376</v>
+        <v>-10.51711048326244</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.113387570466755</v>
+        <v>-1.048140170796692</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.647098976321858</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.91225790217386</v>
+        <v>-10.7491394029987</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.203505409732145</v>
+        <v>-1.138258010062082</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.709111673510281</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.86024238820505</v>
+        <v>-10.69712388902989</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.178708868458219</v>
+        <v>-1.113461468788155</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.709111673510281</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.00191422992917</v>
+        <v>-10.83879573075401</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.236852832046608</v>
+        <v>-1.171605432376545</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.709111673510281</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.95232338550434</v>
+        <v>-10.78920488632918</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.201963084111803</v>
+        <v>-1.136715684441739</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.659520829085447</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.75317127826724</v>
+        <v>-10.59005277909208</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.135353374863646</v>
+        <v>-1.070105975193582</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.494198303135634</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.52732612554783</v>
+        <v>-10.36420762637267</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.035436240739674</v>
+        <v>-0.9701888410696102</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.45227162754847</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.40274746921023</v>
+        <v>-10.23962897003508</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9844656336485778</v>
+        <v>-0.9192182339785142</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.45227162754847</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.45564275725452</v>
+        <v>-10.29252425807936</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.002989974704184</v>
+        <v>-0.9377425750341208</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.447316281460024</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.17173402632577</v>
+        <v>-10.00861552715061</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8836927780940487</v>
+        <v>-0.8184453784239851</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.447316281460024</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.10036763371613</v>
+        <v>-9.937249134540966</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8648834834440553</v>
+        <v>-0.7996360837739913</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.375949888850376</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.836530766512055</v>
+        <v>-9.673412267336897</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7692322178753348</v>
+        <v>-0.7039848182052713</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.375949888850376</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.569288965643658</v>
+        <v>-9.406170466468499</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6641700580273491</v>
+        <v>-0.5989226583572855</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.375949888850376</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781941</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.471381926967167</v>
+        <v>-9.308263427792008</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6253075575302138</v>
+        <v>-0.5600601578601503</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.30796413898982</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567235</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.447428385991209</v>
+        <v>-9.28430988681605</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6150576349943369</v>
+        <v>-0.5498102353242733</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.284010598013862</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487765</v>
+        <v>3.789307536487764</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.183368447668412</v>
+        <v>-9.020249948493253</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5226939758269706</v>
+        <v>-0.4574465761569071</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.019950659691066</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309717</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.476288824163575</v>
+        <v>-8.313170324988416</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2426491600853362</v>
+        <v>-0.1774017604152727</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.019950659691066</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858721</v>
+        <v>3.839370871858719</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.436104525797385</v>
+        <v>-8.272986026622226</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2262318168510187</v>
+        <v>-0.1609844171809551</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.979766361324875</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096466</v>
+        <v>3.856158176096464</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.35603473025958</v>
+        <v>-8.192916231084421</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1948370774151402</v>
+        <v>-0.1295896777450767</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.899696565787071</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.122553508029981</v>
+        <v>-7.959435008854823</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.0935201596854478</v>
+        <v>-0.0282727600153847</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.666215343557473</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255782</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.972887117022466</v>
+        <v>-7.809768617847308</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.0365458135954011</v>
+        <v>0.028701586074662</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.573311852314937</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.840611643391579</v>
+        <v>-7.677493144216421</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.0117318626039804</v>
+        <v>0.0769792622740435</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.44103637868405</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.650011968718426</v>
+        <v>-7.486893469543269</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09078679316087834</v>
+        <v>0.1560341928309414</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.250436704010897</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.401012170034845</v>
+        <v>-7.237893670859687</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2032930538579696</v>
+        <v>0.2685404535280327</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.250436704010897</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.50660215980795</v>
+        <v>-7.343483660632792</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03308112834950894</v>
+        <v>0.09832852801957204</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.356026693784002</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.525337061926547</v>
+        <v>-7.362218562751389</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07413150937915658</v>
+        <v>0.1393789090492197</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.356026693784002</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.377397020518948</v>
+        <v>-7.21427852134379</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01342860325402873</v>
+        <v>0.07867600292409183</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.335705777875444</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.360238870387653</v>
+        <v>-7.197120371212495</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01157787705306834</v>
+        <v>0.07682527672313144</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.31854762774415</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.316690463616963</v>
+        <v>-7.153571964441805</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02203662766625136</v>
+        <v>0.08728402733631446</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.31854762774415</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.074542070163105</v>
+        <v>-6.911423570987947</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1333583394289377</v>
+        <v>0.1986057390990008</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.31854762774415</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.011312698394756</v>
+        <v>-6.848194199219598</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1531822085954717</v>
+        <v>0.2184296082655353</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.31854762774415</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.888021563577626</v>
+        <v>-6.724903064402468</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1999967565329013</v>
+        <v>0.2652441562029644</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.195256492927019</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.866872364674182</v>
+        <v>-6.703753865499024</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2161574143316036</v>
+        <v>0.2814048140016667</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.174107294023576</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.623106922690738</v>
+        <v>-6.45998842351558</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3094442994720321</v>
+        <v>0.3746916991420952</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.174107294023576</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.476209894972868</v>
+        <v>-6.313091395797709</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3703274244791959</v>
+        <v>0.4355748241492594</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.126449052044988</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749179</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.226359501023794</v>
+        <v>-6.063241001848635</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4630096570425279</v>
+        <v>0.5282570567125915</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.126449052044988</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.050467408556361</v>
+        <v>-5.887348909381203</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5369656175501496</v>
+        <v>0.6022130172202131</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.126449052044988</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.879020945533898</v>
+        <v>-5.715902446358739</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6188717088136886</v>
+        <v>0.6841191084837521</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.9550025890225248</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102774</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.653987945865075</v>
+        <v>-5.490869446689916</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7079053862975146</v>
+        <v>0.7731527859675782</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.7299695893537019</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353066</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.590352203631141</v>
+        <v>-5.427233704455982</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.738054484245406</v>
+        <v>0.8033018839154695</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.6663338471197674</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544775</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.497352162425242</v>
+        <v>-5.334233663250084</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.756448759511561</v>
+        <v>0.8216961591816245</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6663338471197674</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712285</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.256921665620382</v>
+        <v>-5.093803166445223</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8543640348583823</v>
+        <v>0.9196114345284458</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.4259033503149071</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837675</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.184679097449187</v>
+        <v>-5.021560598274029</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8871903759616804</v>
+        <v>0.9524377756317439</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.4259033503149071</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.822323422349957</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.1316807751678</v>
+        <v>-4.968562275992641</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9090682887915755</v>
+        <v>0.9743156884616391</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3705670913129683</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972331</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.022875889688073</v>
+        <v>-4.859757390512914</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.94958831420346</v>
+        <v>1.014835713873523</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3705670913129683</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.81866537614593</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.802855091651062</v>
+        <v>-4.639736592475903</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.039175670428878</v>
+        <v>1.104423070098942</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.229347246244988</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009942</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.669987402587784</v>
+        <v>-4.506868903412625</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.108216928856013</v>
+        <v>1.173464328526076</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.229347246244988</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.510472299068415</v>
+        <v>-4.347353799893256</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.173168814704062</v>
+        <v>1.238416214374126</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.06983214272561811</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.365800153968677</v>
+        <v>-4.202681654793518</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.241125775305397</v>
+        <v>1.306373174975461</v>
       </c>
       <c r="F1932" t="n">
         <v>0.07484000237411931</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.425674981326369</v>
+        <v>-4.262556482151211</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.203213335763746</v>
+        <v>1.26846073543381</v>
       </c>
       <c r="F1933" t="n">
         <v>0.01496517501642719</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.33887548354736</v>
+        <v>-4.175756984372201</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.260333628197916</v>
+        <v>1.325581027867979</v>
       </c>
       <c r="F1934" t="n">
         <v>0.01496517501642719</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.341345190009166</v>
+        <v>-4.178226690834007</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.259418146986606</v>
+        <v>1.324665546656669</v>
       </c>
       <c r="F1935" t="n">
         <v>0.01249546855462103</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.409715376333176</v>
+        <v>-4.246596877158018</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.243076994931704</v>
+        <v>1.308324394601767</v>
       </c>
       <c r="F1936" t="n">
         <v>0.02177116759083597</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.51825355724931</v>
+        <v>-4.355135058074151</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.190098431197141</v>
+        <v>1.255345830867205</v>
       </c>
       <c r="F1937" t="n">
         <v>0.02177116759083597</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887696</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.549246716578016</v>
+        <v>-4.386128217402857</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.002410732506046</v>
+        <v>1.067658132176109</v>
       </c>
       <c r="F1938" t="n">
         <v>0.02177116759083597</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675892</v>
+        <v>3.74603895067589</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.373772456785547</v>
+        <v>-4.210653957610388</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.077167668414821</v>
+        <v>1.142415068084885</v>
       </c>
       <c r="F1939" t="n">
         <v>0.02177116759083597</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695438</v>
+        <v>3.765020747695436</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.484708709426796</v>
+        <v>-4.321590210251637</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.008535196119529</v>
+        <v>1.073782595789592</v>
       </c>
       <c r="F1940" t="n">
         <v>0.02177116759083597</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.687735286970029</v>
+        <v>-4.52461678779487</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.930455950322141</v>
+        <v>0.9957033499922046</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1812554099523974</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.529809688034736</v>
+        <v>-4.366691188859577</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.003798576328391</v>
+        <v>1.069045975998454</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1812554099523974</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.443566225008358</v>
+        <v>-4.280447725833199</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.033242232112802</v>
+        <v>1.098489631782865</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1812554099523974</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786042</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.44474930965942</v>
+        <v>-4.281630810484261</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.024544773696903</v>
+        <v>1.089792173366966</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.186898458418909</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273188</v>
+        <v>3.753567590273186</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.321621602665337</v>
+        <v>-4.158503103490178</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.074347729527638</v>
+        <v>1.139595129197701</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.186898458418909</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279497</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.228811121214477</v>
+        <v>-4.065692622039318</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.040744613999347</v>
+        <v>1.105992013669411</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.0940879769680496</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030425</v>
+        <v>3.748282241030423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.180248068993447</v>
+        <v>-4.017129569818288</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.06204331081236</v>
+        <v>1.127290710482423</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.04552492474701941</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942737</v>
+        <v>3.721073619942735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.067576850757197</v>
+        <v>-3.904458351582038</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.102187506618583</v>
+        <v>1.167434906288647</v>
       </c>
       <c r="F1948" t="n">
         <v>0.06714629348923079</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268533</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.116933623869789</v>
+        <v>-3.792081350399366</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.087936093204213</v>
+        <v>1.217877002592383</v>
       </c>
       <c r="F1949" t="n">
         <v>0.06714629348923079</v>
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968857</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.31516819275652</v>
+        <v>-3.861784201664709</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.02013946741806</v>
+        <v>1.201493063854784</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1310882753974998</v>
+        <v>-0.002556557776112911</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.667910203595916</v>
+        <v>2.745029234168748</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306604617532</v>
+        <v>3.643066046175317</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.398169473781799</v>
+        <v>-3.944785482689988</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8252946750086019</v>
+        <v>1.006648271445326</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1496591599246735</v>
+        <v>-0.02112744230328667</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.495123392880265</v>
+        <v>2.572242423453097</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199264</v>
+        <v>3.682712735199261</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.525236480088787</v>
+        <v>-4.071852488996976</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8946175332050124</v>
+        <v>1.075971129641737</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1496591599246735</v>
+        <v>-0.02112744230328667</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.61527305359947</v>
+        <v>2.692392084172303</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.73300886566076</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.61183506306989</v>
+        <v>-4.158451071978079</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.874491126114894</v>
+        <v>1.055844722551619</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1496591599246735</v>
+        <v>-0.02112744230328667</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.629786079701793</v>
+        <v>2.706905110274626</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383418</v>
+        <v>3.741170494383415</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.573451400511739</v>
+        <v>-4.120067409419928</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8872640324805232</v>
+        <v>1.068617628917248</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1112754973665224</v>
+        <v>0.01725622025486451</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.650235718579053</v>
+        <v>2.727354749151885</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002479</v>
+        <v>3.751143622002476</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.396335070476573</v>
+        <v>-3.942951079384762</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9548395933398917</v>
+        <v>1.136193189776616</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1112754973665224</v>
+        <v>0.01725622025486451</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.646964747424355</v>
+        <v>2.724083777997187</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263896</v>
+        <v>3.741324873263893</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.366632946500279</v>
+        <v>-3.913248955408468</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9674038346923222</v>
+        <v>1.148757431129046</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1157456225818357</v>
+        <v>0.01278609503955114</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.64496606405708</v>
+        <v>2.722085094629912</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481228</v>
+        <v>3.750725801481225</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.187257525261511</v>
+        <v>-3.7338735341697</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.032940978494244</v>
+        <v>1.214294574930968</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04103113558888294</v>
+        <v>0.1695628532102698</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.732819094265925</v>
+        <v>2.809938124838757</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452223</v>
+        <v>3.716988143452221</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.232271738782117</v>
+        <v>-3.778887747690307</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9957427484175909</v>
+        <v>1.177096344854315</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01068224027427833</v>
+        <v>0.1392139578956652</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.695417212408752</v>
+        <v>2.772536242981585</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979527</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.499276249054552</v>
+        <v>-4.045892257962742</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8946325066475627</v>
+        <v>1.075986103084287</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1836807977686702</v>
+        <v>-0.05514908014728337</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.584490951921929</v>
+        <v>2.661609982494761</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230803</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.788063469513467</v>
+        <v>-4.334679478421657</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7783215403604982</v>
+        <v>0.9596751367972221</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2847669178676706</v>
+        <v>-0.1562352002462837</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.52304320175903</v>
+        <v>2.600162232331862</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.755587883342695</v>
+        <v>-4.302203892250885</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7889117363831237</v>
+        <v>0.9702653328198476</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2847669178676706</v>
+        <v>-0.1562352002462837</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.520643163313347</v>
+        <v>2.597762193886179</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.736549755635398</v>
+        <v>-4.283165764543588</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7930517066742875</v>
+        <v>0.9744053031110116</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3429505291988652</v>
+        <v>-0.2144188115774783</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.482257715722875</v>
+        <v>2.559376746295707</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601249</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.767676386786016</v>
+        <v>-4.314292395694206</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9581829231527208</v>
+        <v>1.139536519589445</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3429505291988652</v>
+        <v>-0.2144188115774783</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.659839584661556</v>
+        <v>2.736958615234388</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.819996767386808</v>
+        <v>-4.397759320996251</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9380880998985375</v>
+        <v>1.106983078454761</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.308003669189993</v>
+        <v>-0.2678427967263933</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.681641029653012</v>
+        <v>2.705737553131172</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259118</v>
+        <v>3.787422005259115</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.964319673311727</v>
+        <v>-4.54208222692117</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.886367467925496</v>
+        <v>1.055262446481719</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.308003669189993</v>
+        <v>-0.2678427967263933</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.687649560049938</v>
+        <v>2.711746083528098</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989903</v>
+        <v>3.7814976749899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.816576703076724</v>
+        <v>-4.394339256686167</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.024617303811519</v>
+        <v>1.193512282367742</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1401963119551098</v>
+        <v>-0.1000354394915102</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.86748662218289</v>
+        <v>2.89158314566105</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651165</v>
+        <v>3.802242353651161</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.918591385607946</v>
+        <v>-4.496353939217388</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9866050523305114</v>
+        <v>1.155500030886734</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1401963119551098</v>
+        <v>-0.1000354394915102</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.870280243714371</v>
+        <v>2.894376767192531</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864723</v>
+        <v>3.80560540986472</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.781982041513853</v>
+        <v>-4.359744595123296</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.041911138359807</v>
+        <v>1.21080611691603</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.003586967861017365</v>
+        <v>0.03657390460258231</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.952908198562485</v>
+        <v>2.977004722040645</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360611</v>
+        <v>3.798236219360607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.924747374336503</v>
+        <v>-4.502509927945946</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9838854819708569</v>
+        <v>1.15278046052708</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1463523006836678</v>
+        <v>-0.1061914282200681</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.866329475609005</v>
+        <v>2.890425999087165</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268422</v>
+        <v>3.867359061268418</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.903634401948034</v>
+        <v>-4.440211929169823</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.058666224723065</v>
+        <v>1.24403521383435</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1463523006836678</v>
+        <v>-0.1061914282200681</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.932665029405826</v>
+        <v>2.956761552883986</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462185</v>
+        <v>3.848725564462182</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.701844204282876</v>
+        <v>-4.238421731504666</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8479631761785267</v>
+        <v>1.033332165289811</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.05166589148548661</v>
+        <v>0.09182676394908629</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.760056817096717</v>
+        <v>2.784153340574877</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144124232242</v>
+        <v>3.841441242322416</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.641953522640283</v>
+        <v>-4.178531049862072</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9422096811577392</v>
+        <v>1.127578670269024</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1115565731280801</v>
+        <v>0.1517174455916798</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.866281458404448</v>
+        <v>2.890377981882608</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.739694067265257</v>
+        <v>-4.276271594487047</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.917741199423793</v>
+        <v>1.103110188535077</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.09566729499509991</v>
+        <v>0.1358281674586996</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.871375627640703</v>
+        <v>2.895472151118863</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.449122134360777</v>
+        <v>3.847910029752606</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.60141803624519</v>
+        <v>2.857747737001229</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.739694067265257</v>
+        <v>-4.276271594487047</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.917741199423793</v>
+        <v>1.103110188535077</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.09566729499509991</v>
+        <v>0.1358281674586996</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.594481833231558</v>
+        <v>2.850811533987597</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-56.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>444.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-589.2%</t>
+          <t>-613.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-265.9%</t>
+          <t>-275.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>199.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-284.1%</t>
+          <t>-288.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.4%</t>
+          <t>-238.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-191.6%</t>
         </is>
       </c>
     </row>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781941</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567235</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487764</v>
+        <v>3.789307536487765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309717</v>
+        <v>3.833249172309719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858719</v>
+        <v>3.839370871858721</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096464</v>
+        <v>3.856158176096466</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255782</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749179</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102774</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353066</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544775</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712285</v>
+        <v>3.797691308712286</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837675</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349957</v>
+        <v>3.822323422349958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972331</v>
+        <v>3.848613050972332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614593</v>
+        <v>3.818665376145931</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009942</v>
+        <v>3.843270952009943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.74603895067589</v>
+        <v>3.746038950675891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968857</v>
+        <v>3.689594264968858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.861784201664709</v>
+        <v>-3.990315919286096</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.201493063854784</v>
+        <v>1.15008037680623</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.002556557776112911</v>
+        <v>-0.1310882753974998</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.745029234168748</v>
+        <v>2.667910203595916</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.944785482689988</v>
+        <v>-4.07648565897536</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.006648271445326</v>
+        <v>0.9539682009311776</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.02112744230328667</v>
+        <v>-0.2098290558700435</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.572242423453097</v>
+        <v>2.459021455313043</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199261</v>
+        <v>3.682712735199262</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.071852488996976</v>
+        <v>-4.168507066298074</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.075971129641737</v>
+        <v>1.037309298721298</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.02112744230328667</v>
+        <v>-0.2098290558700435</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.692392084172303</v>
+        <v>2.579171116032248</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566076</v>
+        <v>3.733008865660761</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.158451071978079</v>
+        <v>-4.255105649279177</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.055844722551619</v>
+        <v>1.017182891631179</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.02112744230328667</v>
+        <v>-0.2098290558700435</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.706905110274626</v>
+        <v>2.593684142134571</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383415</v>
+        <v>3.741170494383416</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.120067409419928</v>
+        <v>-4.216721986721025</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.068617628917248</v>
+        <v>1.029955797996809</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.01725622025486451</v>
+        <v>-0.1714453933118923</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.727354749151885</v>
+        <v>2.614133781011831</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002476</v>
+        <v>3.751143622002477</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.942951079384762</v>
+        <v>-4.039605656685859</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.136193189776616</v>
+        <v>1.097531358856177</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.01725622025486451</v>
+        <v>-0.1714453933118923</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.724083777997187</v>
+        <v>2.610862809857133</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263893</v>
+        <v>3.741324873263894</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.913248955408468</v>
+        <v>-4.009903532709566</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.148757431129046</v>
+        <v>1.110095600208608</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.01278609503955114</v>
+        <v>-0.1759155185272057</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.722085094629912</v>
+        <v>2.608864126489858</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481225</v>
+        <v>3.750725801481226</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.7338735341697</v>
+        <v>-3.830528111470798</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.214294574930968</v>
+        <v>1.175632744010529</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1695628532102698</v>
+        <v>-0.01913876035648704</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.809938124838757</v>
+        <v>2.696717156698703</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.778887747690307</v>
+        <v>-3.875542324991404</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.177096344854315</v>
+        <v>1.138434513933876</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1392139578956652</v>
+        <v>-0.04948765567109165</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.772536242981585</v>
+        <v>2.65931527484153</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.045892257962742</v>
+        <v>-4.14254683526384</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.075986103084287</v>
+        <v>1.037324272163848</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.05514908014728337</v>
+        <v>-0.2438506937140402</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.661609982494761</v>
+        <v>2.548389014354707</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.334679478421657</v>
+        <v>-4.431334055722755</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9596751367972221</v>
+        <v>0.9210133058767831</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1562352002462837</v>
+        <v>-0.3449368138130406</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.600162232331862</v>
+        <v>2.486941264191808</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.302203892250885</v>
+        <v>-4.398858469551983</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9702653328198476</v>
+        <v>0.9316035018994087</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1562352002462837</v>
+        <v>-0.3449368138130406</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.597762193886179</v>
+        <v>2.484541225746125</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.283165764543588</v>
+        <v>-4.379820341844685</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9744053031110116</v>
+        <v>0.9357434721905724</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2144188115774783</v>
+        <v>-0.4031204251442351</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.559376746295707</v>
+        <v>2.446155778155653</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.314292395694206</v>
+        <v>-4.410946972995304</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.139536519589445</v>
+        <v>1.100874688669006</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2144188115774783</v>
+        <v>-0.4031204251442351</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.736958615234388</v>
+        <v>2.623737647094334</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.397759320996251</v>
+        <v>-4.463267353596096</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.106983078454761</v>
+        <v>1.080779865414823</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2678427967263933</v>
+        <v>-0.368173565135363</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.705737553131172</v>
+        <v>2.64553909208579</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.54208222692117</v>
+        <v>-4.607590259521015</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.055262446481719</v>
+        <v>1.029059233441781</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2678427967263933</v>
+        <v>-0.368173565135363</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.711746083528098</v>
+        <v>2.651547622482716</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.394339256686167</v>
+        <v>-4.459847289286012</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.193512282367742</v>
+        <v>1.167309069327804</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1000354394915102</v>
+        <v>-0.2003662079004798</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.89158314566105</v>
+        <v>2.831384684615669</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.496353939217388</v>
+        <v>-4.561861971817233</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.155500030886734</v>
+        <v>1.129296817846796</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1000354394915102</v>
+        <v>-0.2003662079004798</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.894376767192531</v>
+        <v>2.834178306147149</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.359744595123296</v>
+        <v>-4.425252627723141</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.21080611691603</v>
+        <v>1.184602903876092</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.03657390460258231</v>
+        <v>-0.06375686380638734</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.977004722040645</v>
+        <v>2.916806260995263</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.502509927945946</v>
+        <v>-4.568017960545791</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.15278046052708</v>
+        <v>1.126577247487142</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1061914282200681</v>
+        <v>-0.2065221966290378</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.890425999087165</v>
+        <v>2.830227538041783</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.440211929169823</v>
+        <v>-4.505719961769668</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.24403521383435</v>
+        <v>1.217832000794412</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1061914282200681</v>
+        <v>-0.2065221966290378</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.956761552883986</v>
+        <v>2.896563091838604</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.238421731504666</v>
+        <v>-4.478930606970694</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.033332165289811</v>
+        <v>0.9371286151033995</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.09182676394908629</v>
+        <v>-0.1888126115244542</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.784153340574877</v>
+        <v>2.615769715290752</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.178531049862072</v>
+        <v>-4.419039925328101</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.127578670269024</v>
+        <v>1.031375120082612</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1517174455916798</v>
+        <v>-0.1289219298818607</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.890377981882608</v>
+        <v>2.721994356598484</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789552</v>
+        <v>3.819059724789549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.276271594487047</v>
+        <v>-4.516780469953075</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.103110188535077</v>
+        <v>1.006906638348666</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1358281674586996</v>
+        <v>-0.1448112080148409</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.895472151118863</v>
+        <v>2.727088525834739</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.847910029752606</v>
+        <v>3.435091285582651</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.857747737001229</v>
+        <v>2.550732956644223</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.276271594487047</v>
+        <v>-4.516780469953075</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.103110188535077</v>
+        <v>1.006906638348666</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.1358281674586996</v>
+        <v>-0.1448112080148409</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.850811533987597</v>
+        <v>2.543796753630591</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-46.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-667.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.3%</t>
+          <t>448.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-613.3%</t>
+          <t>-625.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-267.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-275.5%</t>
+          <t>-280.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-288.3%</t>
+          <t>-144.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-238.5%</t>
+          <t>-238.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-191.6%</t>
+          <t>-181.4%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.389802307917311</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.381461299082708</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.821608101067098</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.195071869290197</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-5.05630209519965</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.089479046639267</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.391964742430103</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.9537945794030511</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.755590987330416</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.8148316416771673</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.120718369969163</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.6680352036274999</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.529307147149842</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.5033612367699876</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.805883247465674</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.387916229115115</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.222275121752672</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.2193535300091938</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.520777415280859</v>
+        <v>-7.53888706429332</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1102113032665977</v>
+        <v>0.1029674436616133</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.866652237265669</v>
+        <v>-7.884761886278129</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03203906038163096</v>
+        <v>-0.03928291998661537</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.030232115450053</v>
+        <v>-8.048341764462513</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09906609160038382</v>
+        <v>-0.1063099512053678</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.326893457260251</v>
+        <v>-8.345003106272712</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2139516523952549</v>
+        <v>-0.2211955120002389</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.45013784647568</v>
+        <v>-8.468247495488141</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2672757126158296</v>
+        <v>-0.274519572220814</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.833139235218312</v>
+        <v>-8.851248884230772</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.420578369434466</v>
+        <v>-0.4278222290394504</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.990538115431432</v>
+        <v>-9.008647764443893</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4809664055482843</v>
+        <v>-0.4882102651532687</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.350068437935434</v>
+        <v>-9.368178086947895</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6194282312518347</v>
+        <v>-0.6266720908568191</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.400417501389656</v>
+        <v>-9.418527150402117</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6316518366763462</v>
+        <v>-0.6388956962813306</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.498036778811052</v>
+        <v>-9.516146427823513</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6676577970231357</v>
+        <v>-0.6749016566281201</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.494345853854641</v>
+        <v>-9.512455502867102</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6661814270405713</v>
+        <v>-0.6734252866455557</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.698604029184505</v>
+        <v>-9.716713678196966</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7423715000538746</v>
+        <v>-0.7496153596588586</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.840413803391293</v>
+        <v>-9.858523452403753</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7946128552521539</v>
+        <v>-0.8018567148571378</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.161965059483127</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.766943971723844</v>
+        <v>-9.785053620736305</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7498532210917528</v>
+        <v>-0.7570970806967372</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.088495227815679</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.942068389110387</v>
+        <v>-9.960178038122848</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8053477672988536</v>
+        <v>-0.8125916269038376</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.263619645202223</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.17652048312488</v>
+        <v>-10.19463013213734</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9063477698062452</v>
+        <v>-0.9135916294112296</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.263619645202223</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.46432432766212</v>
+        <v>-10.48243397667458</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.028141498395117</v>
+        <v>-1.035385358000101</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.551423489739461</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.51711048326244</v>
+        <v>-10.5352201322749</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.048140170796692</v>
+        <v>-1.055384030401676</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.647098976321858</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.7491394029987</v>
+        <v>-10.76724905201116</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.138258010062082</v>
+        <v>-1.145501869667065</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.709111673510281</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.69712388902989</v>
+        <v>-10.71523353804235</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.113461468788155</v>
+        <v>-1.120705328393139</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.709111673510281</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.83879573075401</v>
+        <v>-10.85690537976647</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.171605432376545</v>
+        <v>-1.178849291981529</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.709111673510281</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.78920488632918</v>
+        <v>-10.80731453534164</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.136715684441739</v>
+        <v>-1.143959544046723</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.659520829085447</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.59005277909208</v>
+        <v>-10.60816242810454</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.070105975193582</v>
+        <v>-1.077349834798567</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.494198303135634</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.36420762637267</v>
+        <v>-10.38231727538513</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9701888410696102</v>
+        <v>-0.9774327006745938</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.45227162754847</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.23962897003508</v>
+        <v>-10.25773861904753</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9192182339785142</v>
+        <v>-0.9264620935834977</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.45227162754847</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.29252425807936</v>
+        <v>-10.31063390709182</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9377425750341208</v>
+        <v>-0.9449864346391044</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.447316281460024</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.00861552715061</v>
+        <v>-10.02672517616307</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8184453784239851</v>
+        <v>-0.8256892380289687</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.447316281460024</v>
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.937249134540966</v>
+        <v>-10.00489821320857</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7996360837739913</v>
+        <v>-0.8266957152410321</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.375949888850376</v>
+        <v>-2.425489318505519</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.750050061045917</v>
+        <v>1.720326403252831</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.673412267336897</v>
+        <v>-9.741061346004498</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7039848182052713</v>
+        <v>-0.7310444496723116</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.375949888850376</v>
+        <v>-2.425489318505519</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.740166579733009</v>
+        <v>1.710442921939924</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.406170466468499</v>
+        <v>-9.4738195451361</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5989226583572855</v>
+        <v>-0.6259822898243264</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.375949888850376</v>
+        <v>-2.425489318505519</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.738332019233636</v>
+        <v>1.70860836144055</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.308263427792008</v>
+        <v>-9.37591250645961</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5600601578601503</v>
+        <v>-0.5871197893271911</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.30796413898982</v>
+        <v>-2.357503568644963</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.778823154176509</v>
+        <v>1.749099496383423</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.28430988681605</v>
+        <v>-9.351958965483652</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5498102353242733</v>
+        <v>-0.5768698667913141</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.284010598013862</v>
+        <v>-2.333550027669005</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.793863784907577</v>
+        <v>1.764140127114491</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.020249948493253</v>
+        <v>-9.087899027160855</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4574465761569071</v>
+        <v>-0.4845062076239475</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.019950659691066</v>
+        <v>-2.069490089346209</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.939039431739502</v>
+        <v>1.909315773946417</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.313170324988416</v>
+        <v>-8.380819403656018</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1774017604152727</v>
+        <v>-0.2044613918823135</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.019950659691066</v>
+        <v>-2.069490089346209</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.936252398079201</v>
+        <v>1.906528740286116</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.272986026622226</v>
+        <v>-8.340635105289827</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1609844171809551</v>
+        <v>-0.188044048647996</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.979766361324875</v>
+        <v>-2.029305790980018</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.960706600986757</v>
+        <v>1.930982943193672</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.192916231084421</v>
+        <v>-8.260565309752023</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1295896777450767</v>
+        <v>-0.1566493092121171</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.899696565787071</v>
+        <v>-1.949235995442214</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.008115299530197</v>
+        <v>1.978391641737111</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.959435008854823</v>
+        <v>-8.027084087522425</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.0282727600153847</v>
+        <v>-0.05533239148242597</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.666215343557473</v>
+        <v>-1.715754773212616</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.156128461705808</v>
+        <v>2.126404803912723</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.809768617847308</v>
+        <v>-7.87741769651491</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.028701586074662</v>
+        <v>0.001641954607621177</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.573311852314937</v>
+        <v>-1.62285128197008</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.208978346138371</v>
+        <v>2.179254688345285</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.677493144216421</v>
+        <v>-7.745142222884024</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.0769792622740435</v>
+        <v>0.04991963080700268</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.44103637868405</v>
+        <v>-1.490575808339193</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.283711117063929</v>
+        <v>2.253987459270844</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.486893469543269</v>
+        <v>-7.554542548210871</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1560341928309414</v>
+        <v>0.1289745613639006</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.250436704010897</v>
+        <v>-1.29997613366604</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.400885982555458</v>
+        <v>2.371162324762373</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.237893670859687</v>
+        <v>-7.30554274952729</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2685404535280327</v>
+        <v>0.2414808220609914</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.250436704010897</v>
+        <v>-1.29997613366604</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.413792323779117</v>
+        <v>2.384068665986031</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.343483660632792</v>
+        <v>-7.411132739300395</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.09832852801957204</v>
+        <v>0.07126889655253121</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.356026693784002</v>
+        <v>-1.405566123439145</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.222462400316036</v>
+        <v>2.19273874252295</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.362218562751389</v>
+        <v>-7.429867641418991</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1393789090492197</v>
+        <v>0.1123192775821789</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.356026693784002</v>
+        <v>-1.405566123439145</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.271006742193122</v>
+        <v>2.241283084400036</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.21427852134379</v>
+        <v>-7.281927600011392</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07867600292409183</v>
+        <v>0.051616371457051</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.335705777875444</v>
+        <v>-1.385245207530587</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.163320369050089</v>
+        <v>2.133596711257003</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.197120371212495</v>
+        <v>-7.264769449880098</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07682527672313144</v>
+        <v>0.04976564525609017</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.368087057399293</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.164901272875387</v>
+        <v>2.135177615082302</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.153571964441805</v>
+        <v>-7.221221043109407</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08728402733631446</v>
+        <v>0.0602243958692732</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.368087057399293</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.157940660780294</v>
+        <v>2.128217002987209</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.911423570987947</v>
+        <v>-6.979072649655549</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1986057390990008</v>
+        <v>0.1715461076319595</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.368087057399293</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.172403015161437</v>
+        <v>2.142679357368352</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.848194199219598</v>
+        <v>-6.915843277887201</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2184296082655353</v>
+        <v>0.191369976798494</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.31854762774415</v>
+        <v>-1.368087057399293</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.166935135620632</v>
+        <v>2.137211477827547</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.724903064402468</v>
+        <v>-6.79255214307007</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2652441562029644</v>
+        <v>0.2381845247359231</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.195256492927019</v>
+        <v>-1.244795922582162</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.238407910521488</v>
+        <v>2.208684252728402</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.703753865499024</v>
+        <v>-6.771402944166627</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2814048140016667</v>
+        <v>0.2543451825346259</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.174107294023576</v>
+        <v>-1.223646723678719</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.258798408100879</v>
+        <v>2.229074750307793</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.45998842351558</v>
+        <v>-6.527637502183183</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3746916991420952</v>
+        <v>0.3476320676750544</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.174107294023576</v>
+        <v>-1.223646723678719</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.254579116447929</v>
+        <v>2.224855458654844</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.313091395797709</v>
+        <v>-6.380740474465313</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4355748241492594</v>
+        <v>0.4085151926822181</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.126449052044988</v>
+        <v>-1.175988481700131</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.285298375555098</v>
+        <v>2.255574717762013</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.063241001848635</v>
+        <v>-6.130890080516238</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5282570567125915</v>
+        <v>0.5011974252455502</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.126449052044988</v>
+        <v>-1.175988481700131</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.2780404505388</v>
+        <v>2.248316792745714</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.887348909381203</v>
+        <v>-5.954997988048806</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6022130172202131</v>
+        <v>0.5751533857531719</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.126449052044988</v>
+        <v>-1.175988481700131</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.281639574059449</v>
+        <v>2.251915916266364</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.715902446358739</v>
+        <v>-5.783551525026343</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6841191084837521</v>
+        <v>0.6570594770167109</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9550025890225248</v>
+        <v>-1.004542018677668</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.39783495792748</v>
+        <v>2.368111300134395</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.490869446689916</v>
+        <v>-5.753240851657608</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7731527859675782</v>
+        <v>0.6682042239805015</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7299695893537019</v>
+        <v>-0.9742313453089332</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.531875235345071</v>
+        <v>2.385318181771932</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.427233704455982</v>
+        <v>-5.689605109423674</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8033018839154695</v>
+        <v>0.6983533219283924</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6663338471197674</v>
+        <v>-0.9105956030749986</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.574751481739749</v>
+        <v>2.428194428166611</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.334233663250084</v>
+        <v>-5.596605068217776</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8216961591816245</v>
+        <v>0.7167475971945474</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6663338471197674</v>
+        <v>-0.9105956030749986</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.555945740523545</v>
+        <v>2.409388686950406</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712286</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.093803166445223</v>
+        <v>-5.356174571412915</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9196114345284458</v>
+        <v>0.8146628725413692</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4259033503149071</v>
+        <v>-0.6701651062701384</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.701947115231338</v>
+        <v>2.5553900616582</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.021560598274029</v>
+        <v>-5.283932003241721</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9524377756317439</v>
+        <v>0.8474892136446672</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4259033503149071</v>
+        <v>-0.6701651062701384</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.705876429066159</v>
+        <v>2.55931937549302</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.968562275992641</v>
+        <v>-5.230933680960333</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9743156884616391</v>
+        <v>0.8693671264745624</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3705670913129683</v>
+        <v>-0.6148288472681995</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.739756768384662</v>
+        <v>2.593199714811523</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.859757390512914</v>
+        <v>-5.122128795480606</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.014835713873523</v>
+        <v>0.9098871518864464</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3705670913129683</v>
+        <v>-0.6148288472681995</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.736754839604655</v>
+        <v>2.590197786031517</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.639736592475903</v>
+        <v>-4.902107997443595</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.104423070098942</v>
+        <v>0.9994745081118648</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.229347246244988</v>
+        <v>-0.4736090022002193</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.823065783656058</v>
+        <v>2.676508730082919</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.506868903412625</v>
+        <v>-4.769240308380318</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.173464328526076</v>
+        <v>1.068515766538999</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.229347246244988</v>
+        <v>-0.4736090022002193</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.838959966457881</v>
+        <v>2.692402912884742</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.347353799893256</v>
+        <v>-4.609725204860948</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.238416214374126</v>
+        <v>1.133467652387049</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06983214272561811</v>
+        <v>-0.3140938986808494</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.935814873009805</v>
+        <v>2.789257819436666</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.202681654793518</v>
+        <v>-4.46505305976121</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.306373174975461</v>
+        <v>1.201424612988384</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.07484000237411931</v>
+        <v>-0.1694217535811119</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.032706262631087</v>
+        <v>2.886149209057948</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.262556482151211</v>
+        <v>-4.524927887118903</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.26846073543381</v>
+        <v>1.163512173446733</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.01496517501642719</v>
+        <v>-0.2292965809388041</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.982818857617898</v>
+        <v>2.836261804044759</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.175756984372201</v>
+        <v>-4.438128389339894</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.325581027867979</v>
+        <v>1.220632465880902</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.01496517501642719</v>
+        <v>-0.2292965809388041</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.005219350940464</v>
+        <v>2.858662297367325</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.178226690834007</v>
+        <v>-4.4405980958017</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.324665546656669</v>
+        <v>1.219716984669592</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01249546855462103</v>
+        <v>-0.2317662874006102</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.003809928436792</v>
+        <v>2.857252874863653</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.246596877158018</v>
+        <v>-4.508968282125711</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.308324394601767</v>
+        <v>1.20337583261469</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.2224905883643953</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.020382270333223</v>
+        <v>2.873825216760085</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.355135058074151</v>
+        <v>-4.617506463041845</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.255345830867205</v>
+        <v>1.150397268880128</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.2224905883643953</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.010818978965114</v>
+        <v>2.864261925391976</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887696</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.386128217402857</v>
+        <v>-4.64849962237055</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.067658132176109</v>
+        <v>0.9627095701890322</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.2224905883643953</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.835528544005501</v>
+        <v>2.688971490432363</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.74603895067589</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.210653957610388</v>
+        <v>-4.473025362578081</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.142415068084885</v>
+        <v>1.037466506097807</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.2224905883643953</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.840095775997289</v>
+        <v>2.69353872242415</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.321590210251637</v>
+        <v>-4.58396161521933</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.073782595789592</v>
+        <v>0.968834033802515</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02177116759083597</v>
+        <v>-0.2224905883643953</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.815837804758496</v>
+        <v>2.669280751185358</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.52461678779487</v>
+        <v>-4.786988192762563</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9957033499922046</v>
+        <v>0.8907547880051272</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1812554099523974</v>
+        <v>-0.4255171659076287</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.697153243452462</v>
+        <v>2.550596189879323</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.366691188859577</v>
+        <v>-4.62906259382727</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.069045975998454</v>
+        <v>0.9640974140113769</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1812554099523974</v>
+        <v>-0.4255171659076287</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.707325629884594</v>
+        <v>2.560768576311455</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.280447725833199</v>
+        <v>-4.542819130800893</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.098489631782865</v>
+        <v>0.9935410697957883</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1812554099523974</v>
+        <v>-0.4255171659076287</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.702271900458455</v>
+        <v>2.555714846885316</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.281630810484261</v>
+        <v>-4.544002215451954</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.089792173366966</v>
+        <v>0.9848436113798893</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.186898458418909</v>
+        <v>-0.4311602143741402</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.690661846823073</v>
+        <v>2.544104793249934</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.158503103490178</v>
+        <v>-4.420874508457871</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.139595129197701</v>
+        <v>1.034646567210624</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.186898458418909</v>
+        <v>-0.4311602143741402</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.691213719856175</v>
+        <v>2.544656666283036</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.065692622039318</v>
+        <v>-4.328064027007011</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.105992013669411</v>
+        <v>1.001043451682333</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.0940879769680496</v>
+        <v>-0.3383497329232809</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.676172700618056</v>
+        <v>2.529615647044917</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.017129569818288</v>
+        <v>-4.279500974785981</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.127290710482423</v>
+        <v>1.022342148495346</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.04552492474701941</v>
+        <v>-0.2897866807022507</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.707184007875275</v>
+        <v>2.560626954302136</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.904458351582038</v>
+        <v>-4.166829756549731</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.167434906288647</v>
+        <v>1.062486344301569</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.06714629348923079</v>
+        <v>-0.1771154624660005</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.769862447328748</v>
+        <v>2.623305393755609</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.792081350399366</v>
+        <v>-4.054452755367058</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.217877002592383</v>
+        <v>1.112928440605306</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.06714629348923079</v>
+        <v>-0.1771154624660005</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.775353743159415</v>
+        <v>2.628796689586276</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.990315919286096</v>
+        <v>-4.252687324253789</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.15008037680623</v>
+        <v>1.045131814819153</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1310882753974998</v>
+        <v>-0.375350031352731</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.667910203595916</v>
+        <v>2.521353150022777</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.07648565897536</v>
+        <v>-4.335688605279068</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9539682009311776</v>
+        <v>0.8502870224096943</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2098290558700435</v>
+        <v>-0.3939209158799048</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.459021455313043</v>
+        <v>2.348566339307126</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199262</v>
+        <v>3.682712735199263</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.168507066298074</v>
+        <v>-4.462755611586056</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.037309298721298</v>
+        <v>0.9196098806061046</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2098290558700435</v>
+        <v>-0.3939209158799048</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.579171116032248</v>
+        <v>2.468716000026332</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660761</v>
+        <v>3.733008865660762</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.255105649279177</v>
+        <v>-4.549354194567159</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.017182891631179</v>
+        <v>0.8994834735159865</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2098290558700435</v>
+        <v>-0.3939209158799048</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.593684142134571</v>
+        <v>2.483229026128655</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383416</v>
+        <v>3.741170494383417</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.216721986721025</v>
+        <v>-4.510970532009008</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.029955797996809</v>
+        <v>0.9122563798816157</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1714453933118923</v>
+        <v>-0.3555372533217536</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.614133781011831</v>
+        <v>2.503678665005914</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.039605656685859</v>
+        <v>-4.333854201973842</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.097531358856177</v>
+        <v>0.9798319407409839</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1714453933118923</v>
+        <v>-0.3555372533217536</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.610862809857133</v>
+        <v>2.500407693851216</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.009903532709566</v>
+        <v>-4.304152077997548</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.110095600208608</v>
+        <v>0.9923961820934144</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1759155185272057</v>
+        <v>-0.360007378537067</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.608864126489858</v>
+        <v>2.498409010483941</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481226</v>
+        <v>3.750725801481225</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.830528111470798</v>
+        <v>-4.12477665675878</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.175632744010529</v>
+        <v>1.057933325895336</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01913876035648704</v>
+        <v>-0.2032306203663483</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.696717156698703</v>
+        <v>2.586262040692787</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.875542324991404</v>
+        <v>-4.169790870279387</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.138434513933876</v>
+        <v>1.020735095818683</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.04948765567109165</v>
+        <v>-0.2335795156809529</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.65931527484153</v>
+        <v>2.548860158835614</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.14254683526384</v>
+        <v>-4.436795380551822</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.037324272163848</v>
+        <v>0.9196248540486547</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2438506937140402</v>
+        <v>-0.4279425537239015</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.548389014354707</v>
+        <v>2.43793389834879</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.431334055722755</v>
+        <v>-4.725582601010737</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9210133058767831</v>
+        <v>0.8033138877615902</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3449368138130406</v>
+        <v>-0.5290286738229019</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.486941264191808</v>
+        <v>2.376486148185891</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.398858469551983</v>
+        <v>-4.693107014839965</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9316035018994087</v>
+        <v>0.8139040837842157</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3449368138130406</v>
+        <v>-0.5290286738229019</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.484541225746125</v>
+        <v>2.374086109740208</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.379820341844685</v>
+        <v>-4.674068887132668</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9357434721905724</v>
+        <v>0.8180440540753795</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4031204251442351</v>
+        <v>-0.5872122851540964</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.446155778155653</v>
+        <v>2.335700662149736</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.410946972995304</v>
+        <v>-4.705195518283286</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.100874688669006</v>
+        <v>0.9831752705538128</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4031204251442351</v>
+        <v>-0.5872122851540964</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.623737647094334</v>
+        <v>2.513282531088417</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.463267353596096</v>
+        <v>-4.757515898884078</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.080779865414823</v>
+        <v>0.9630804472996295</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.368173565135363</v>
+        <v>-0.5522654251452243</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.64553909208579</v>
+        <v>2.535083976079874</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.607590259521015</v>
+        <v>-4.901838804808997</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.029059233441781</v>
+        <v>0.9113598153265881</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.368173565135363</v>
+        <v>-0.5522654251452243</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.651547622482716</v>
+        <v>2.5410925064768</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.7814976749899</v>
+        <v>3.781497674989899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.459847289286012</v>
+        <v>-4.754095834573994</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.167309069327804</v>
+        <v>1.049609651212611</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2003662079004798</v>
+        <v>-0.3844580679103411</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.831384684615669</v>
+        <v>2.720929568609752</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651161</v>
+        <v>3.80224235365116</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.561861971817233</v>
+        <v>-4.856110517105216</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.129296817846796</v>
+        <v>1.011597399731603</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2003662079004798</v>
+        <v>-0.3844580679103411</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.834178306147149</v>
+        <v>2.723723190141233</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560540986472</v>
+        <v>3.805605409864719</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.425252627723141</v>
+        <v>-4.719501173011123</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.184602903876092</v>
+        <v>1.066903485760899</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.06375686380638734</v>
+        <v>-0.2478487238162486</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.916806260995263</v>
+        <v>2.806351144989347</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.568017960545791</v>
+        <v>-4.862266505833773</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.126577247487142</v>
+        <v>1.008877829371949</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2065221966290378</v>
+        <v>-0.390614056638899</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.830227538041783</v>
+        <v>2.719772422035867</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.505719961769668</v>
+        <v>-4.799968507057651</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.217832000794412</v>
+        <v>1.100132582679219</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2065221966290378</v>
+        <v>-0.390614056638899</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.896563091838604</v>
+        <v>2.786107975832687</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.478930606970694</v>
+        <v>-4.598178309392493</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9371286151033995</v>
+        <v>0.8894295341346801</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1888126115244542</v>
+        <v>-0.1925958644697446</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.615769715290752</v>
+        <v>2.613499763523578</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322416</v>
+        <v>3.841441242322415</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.419039925328101</v>
+        <v>-4.5382876277499</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.031375120082612</v>
+        <v>0.9836760391138926</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1289219298818607</v>
+        <v>-0.1327051828271512</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.721994356598484</v>
+        <v>2.719724404831309</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789549</v>
+        <v>3.819059724789544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.516780469953075</v>
+        <v>-4.636028172374874</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.006906638348666</v>
+        <v>0.9592075573799463</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1448112080148409</v>
+        <v>-0.1485944609601313</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.727088525834739</v>
+        <v>2.724818574067565</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.435091285582651</v>
+        <v>3.745268518984661</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.550732956644223</v>
+        <v>2.652749136434577</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.516780469953075</v>
+        <v>-4.636028172374874</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.006906638348666</v>
+        <v>0.9592075573799463</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1448112080148409</v>
+        <v>-0.1485944609601313</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.543796753630591</v>
+        <v>2.645812933420945</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-30.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-667.2%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.1%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.2%</t>
+          <t>-593.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-267.3%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.3%</t>
+          <t>-267.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-144.2%</t>
+          <t>-245.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-238.9%</t>
+          <t>-211.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.4%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.389802307917311</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.381461299082708</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.821608101067098</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.195071869290197</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.05630209519965</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.089479046639267</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.391964742430103</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9537945794030511</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.755590987330416</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8148316416771673</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.120718369969163</v>
+        <v>-6.037856068422343</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6680352036274999</v>
+        <v>0.7011801242462279</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-1.072415921171359</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.473229423226098</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.529307147149842</v>
+        <v>-6.446444845603022</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5033612367699876</v>
+        <v>0.5365061573887155</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.481004698352038</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.22683770093245</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.805883247465674</v>
+        <v>-6.784463377737104</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.387916229115115</v>
+        <v>0.3964841770065433</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.481004698352038</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.22202313340391</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.222275121752672</v>
+        <v>-7.200855252024102</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2193535300091938</v>
+        <v>0.2279214779006216</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.481004698352038</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.220017184012788</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.53888706429332</v>
+        <v>-7.51746719456475</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1029674436616133</v>
+        <v>0.1115353915530415</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.481004698352038</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.230275874681467</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.884761886278129</v>
+        <v>-7.863342016549559</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03928291998661537</v>
+        <v>-0.03071497209518714</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.481004698352038</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.226375439827162</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.048341764462513</v>
+        <v>-8.026921894733944</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1063099512053678</v>
+        <v>-0.09774200331394001</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.481004698352038</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.224780359882163</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.345003106272712</v>
+        <v>-8.323583236544142</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2211955120002389</v>
+        <v>-0.2126275641088111</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.549747834085916</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.187313454371044</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.468247495488141</v>
+        <v>-8.446827625759571</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.274519572220814</v>
+        <v>-0.2659516243293858</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.549747834085916</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.18328714983664</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.851248884230772</v>
+        <v>-8.829829014502202</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4278222290394504</v>
+        <v>-0.4192542811480227</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.549747834085916</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.183185048515056</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.008647764443893</v>
+        <v>-8.987227894715323</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4882102651532687</v>
+        <v>-0.4796423172618405</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.707146714299037</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.091317236358614</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.368178086947895</v>
+        <v>-9.346758217219325</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6266720908568191</v>
+        <v>-0.6181041429653913</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.707146714299037</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.096667539656664</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.418527150402117</v>
+        <v>-9.397107280673547</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6388956962813306</v>
+        <v>-0.6303277483899024</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.757495777753259</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>2.074374121541308</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.516146427823513</v>
+        <v>-9.494726558094943</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6749016566281201</v>
+        <v>-0.6663337087366918</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.855115055174656</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.014084948480895</v>
+        <v>2.018844305710239</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.512455502867102</v>
+        <v>-9.491035633138532</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6734252866455557</v>
+        <v>-0.6648573387541279</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.855115055174656</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.014084948480895</v>
+        <v>2.018844305710239</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.716713678196966</v>
+        <v>-9.695293808468396</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7496153596588586</v>
+        <v>-0.7410474117674308</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.990686261837552</v>
+        <v>-1.982753999788645</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.943014778831144</v>
+        <v>1.947774136060488</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.858523452403753</v>
+        <v>-9.837103582675184</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8018567148571378</v>
+        <v>-0.79328876696571</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.161965059483127</v>
+        <v>-2.15403279743422</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.844730054728235</v>
+        <v>1.849489411957579</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.785053620736305</v>
+        <v>-9.763633751007735</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7570970806967372</v>
+        <v>-0.7485291328053094</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.088495227815679</v>
+        <v>-2.080562965766772</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.904183655222125</v>
+        <v>1.908943012451469</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.960178038122848</v>
+        <v>-9.938758168394278</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8125916269038376</v>
+        <v>-0.8040236790124098</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.263619645202223</v>
+        <v>-2.255687383153316</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.813664225537716</v>
+        <v>1.81842358276706</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.19463013213734</v>
+        <v>-10.17321026240877</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9135916294112296</v>
+        <v>-0.9050236815198018</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.263619645202223</v>
+        <v>-2.255687383153316</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.80644506063612</v>
+        <v>1.811204417865464</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.48243397667458</v>
+        <v>-10.46101410694601</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.035385358000101</v>
+        <v>-1.026817410108673</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.551423489739461</v>
+        <v>-2.543491227690554</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.6270905631398</v>
+        <v>1.631849920369145</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.5352201322749</v>
+        <v>-10.51380026254633</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.055384030401676</v>
+        <v>-1.046816082510247</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.647098976321858</v>
+        <v>-2.639166714272951</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.570801061028918</v>
+        <v>1.575560418258263</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.76724905201116</v>
+        <v>-10.74582918228259</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.145501869667065</v>
+        <v>-1.136933921775638</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.709111673510281</v>
+        <v>-2.701179411461374</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.536287171344979</v>
+        <v>1.541046528574323</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.71523353804235</v>
+        <v>-10.69381366831378</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.120705328393139</v>
+        <v>-1.112137380501712</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.709111673510281</v>
+        <v>-2.701179411461374</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.54027750703138</v>
+        <v>1.545036864260724</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.85690537976647</v>
+        <v>-10.8354855100379</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.178849291981529</v>
+        <v>-1.170281344090101</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.709111673510281</v>
+        <v>-2.701179411461374</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.538802280132638</v>
+        <v>1.543561637361982</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.80731453534164</v>
+        <v>-10.78589466561307</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.143959544046723</v>
+        <v>-1.135391596155296</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.659520829085447</v>
+        <v>-2.65158856703654</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.583610196952411</v>
+        <v>1.588369554181755</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.60816242810454</v>
+        <v>-10.58674255837597</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.077349834798567</v>
+        <v>-1.068781886907139</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.494198303135634</v>
+        <v>-2.486266041086727</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.669752578875616</v>
+        <v>1.67451193610496</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.38231727538513</v>
+        <v>-10.36089740565656</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9774327006745938</v>
+        <v>-0.968864752783166</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.45227162754847</v>
+        <v>-2.444339365499563</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.704487657264123</v>
+        <v>1.709247014493467</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.25773861904753</v>
+        <v>-10.23631874931897</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9264620935834977</v>
+        <v>-0.9178941456920708</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.45227162754847</v>
+        <v>-2.444339365499563</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.705626801820182</v>
+        <v>1.710386159049526</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.31063390709182</v>
+        <v>-10.28921403736325</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9449864346391044</v>
+        <v>-0.9364184867476775</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.447316281460024</v>
+        <v>-2.439384019411117</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.711233783635357</v>
+        <v>1.715993140864701</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.02672517616307</v>
+        <v>-10.0053053064345</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8256892380289687</v>
+        <v>-0.8171212901375413</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.447316281460024</v>
+        <v>-2.439384019411117</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.716967487873994</v>
+        <v>1.721726845103338</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.00489821320857</v>
+        <v>-9.933938913824857</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8266957152410321</v>
+        <v>-0.7983119954875475</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.425489318505519</v>
+        <v>-2.368017626801469</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.720326403252831</v>
+        <v>1.754809418275261</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.741061346004498</v>
+        <v>-9.670102046620787</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7310444496723116</v>
+        <v>-0.7026607299188274</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.425489318505519</v>
+        <v>-2.368017626801469</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.710442921939924</v>
+        <v>1.744925936962354</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.4738195451361</v>
+        <v>-9.40286024575239</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6259822898243264</v>
+        <v>-0.5975985700708422</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.425489318505519</v>
+        <v>-2.368017626801469</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.70860836144055</v>
+        <v>1.74309137646298</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.37591250645961</v>
+        <v>-9.304953207075899</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5871197893271911</v>
+        <v>-0.5587360695737065</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.357503568644963</v>
+        <v>-2.300031876940912</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.749099496383423</v>
+        <v>1.783582511405853</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.351958965483652</v>
+        <v>-9.280999666099941</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5768698667913141</v>
+        <v>-0.5484861470378299</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.333550027669005</v>
+        <v>-2.276078335964955</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.764140127114491</v>
+        <v>1.798623142136921</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.087899027160855</v>
+        <v>-9.016939727777144</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4845062076239475</v>
+        <v>-0.4561224878704633</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.069490089346209</v>
+        <v>-2.012018397642159</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.909315773946417</v>
+        <v>1.943798788968847</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.380819403656018</v>
+        <v>-8.309860104272307</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2044613918823135</v>
+        <v>-0.1760776721288293</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.069490089346209</v>
+        <v>-2.012018397642159</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.906528740286116</v>
+        <v>1.941011755308546</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.340635105289827</v>
+        <v>-8.269675805906116</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.188044048647996</v>
+        <v>-0.1596603288945118</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.029305790980018</v>
+        <v>-1.971834099275968</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.930982943193672</v>
+        <v>1.965465958216102</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.260565309752023</v>
+        <v>-8.189606010368312</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1566493092121171</v>
+        <v>-0.1282655894586329</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.949235995442214</v>
+        <v>-1.891764303738164</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.978391641737111</v>
+        <v>2.012874656759541</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.027084087522425</v>
+        <v>-7.956124788138713</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.05533239148242597</v>
+        <v>-0.02694867172894089</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.715754773212616</v>
+        <v>-1.658283081508566</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.126404803912723</v>
+        <v>2.160887818935152</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.87741769651491</v>
+        <v>-7.806458397131198</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.001641954607621177</v>
+        <v>0.03002567436110581</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.62285128197008</v>
+        <v>-1.56537959026603</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.179254688345285</v>
+        <v>2.213737703367715</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.745142222884024</v>
+        <v>-7.674182923500312</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.04991963080700268</v>
+        <v>0.07830335056048732</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.490575808339193</v>
+        <v>-1.433104116635143</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.253987459270844</v>
+        <v>2.288470474293274</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.554542548210871</v>
+        <v>-7.483583248827159</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1289745613639006</v>
+        <v>0.1573582811173853</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.29997613366604</v>
+        <v>-1.24250444196199</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.371162324762373</v>
+        <v>2.405645339784802</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.30554274952729</v>
+        <v>-7.234583450143578</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2414808220609914</v>
+        <v>0.2698645418144765</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.29997613366604</v>
+        <v>-1.24250444196199</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.384068665986031</v>
+        <v>2.418551681008461</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.411132739300395</v>
+        <v>-7.340173439916683</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.07126889655253121</v>
+        <v>0.09965261630601585</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.405566123439145</v>
+        <v>-1.348094431735094</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.19273874252295</v>
+        <v>2.22722175754538</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.429867641418991</v>
+        <v>-7.35890834203528</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1123192775821789</v>
+        <v>0.1407029973356635</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.405566123439145</v>
+        <v>-1.348094431735094</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.241283084400036</v>
+        <v>2.275766099422466</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.281927600011392</v>
+        <v>-7.21096830062768</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.051616371457051</v>
+        <v>0.08000009121053564</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.385245207530587</v>
+        <v>-1.327773515826537</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.133596711257003</v>
+        <v>2.168079726279433</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.264769449880098</v>
+        <v>-7.193810150496386</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.04976564525609017</v>
+        <v>0.07814936500957526</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.368087057399293</v>
+        <v>-1.310615365695243</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.135177615082302</v>
+        <v>2.169660630104731</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.221221043109407</v>
+        <v>-7.150261743725696</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.0602243958692732</v>
+        <v>0.08860811562275828</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.368087057399293</v>
+        <v>-1.310615365695243</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.128217002987209</v>
+        <v>2.162700018009638</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.979072649655549</v>
+        <v>-6.908113350271837</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1715461076319595</v>
+        <v>0.1999298273854446</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.368087057399293</v>
+        <v>-1.310615365695243</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.142679357368352</v>
+        <v>2.177162372390781</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.915843277887201</v>
+        <v>-6.844883978503489</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.191369976798494</v>
+        <v>0.2197536965519786</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.368087057399293</v>
+        <v>-1.310615365695243</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.137211477827547</v>
+        <v>2.171694492849976</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.79255214307007</v>
+        <v>-6.721592843686358</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2381845247359231</v>
+        <v>0.2665682444894082</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.244795922582162</v>
+        <v>-1.187324230878112</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.208684252728402</v>
+        <v>2.243167267750832</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.771402944166627</v>
+        <v>-6.700443644782915</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2543451825346259</v>
+        <v>0.2827289022881105</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.223646723678719</v>
+        <v>-1.166175031974669</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.229074750307793</v>
+        <v>2.263557765330223</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.527637502183183</v>
+        <v>-6.456678202799471</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3476320676750544</v>
+        <v>0.376015787428539</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.223646723678719</v>
+        <v>-1.166175031974669</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.224855458654844</v>
+        <v>2.259338473677274</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.380740474465313</v>
+        <v>-6.3097811750816</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4085151926822181</v>
+        <v>0.4368989124357032</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.175988481700131</v>
+        <v>-1.118516789996081</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.255574717762013</v>
+        <v>2.290057732784442</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.130890080516238</v>
+        <v>-6.059930781132525</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5011974252455502</v>
+        <v>0.5295811449990353</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.175988481700131</v>
+        <v>-1.118516789996081</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.248316792745714</v>
+        <v>2.282799807768145</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.954997988048806</v>
+        <v>-5.884038688665093</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5751533857531719</v>
+        <v>0.603537105506657</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.175988481700131</v>
+        <v>-1.118516789996081</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.251915916266364</v>
+        <v>2.286398931288793</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.783551525026343</v>
+        <v>-5.71259222564263</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6570594770167109</v>
+        <v>0.6854431967701959</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.004542018677668</v>
+        <v>-0.9470703269736175</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.368111300134395</v>
+        <v>2.402594315156825</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.753240851657608</v>
+        <v>-5.487559225973807</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6682042239805015</v>
+        <v>0.774476874254022</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9742313453089332</v>
+        <v>-0.7220373273047946</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.385318181771932</v>
+        <v>2.536634592574416</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.689605109423674</v>
+        <v>-5.423923483739872</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6983533219283924</v>
+        <v>0.8046259722019133</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9105956030749986</v>
+        <v>-0.6584015850708601</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.428194428166611</v>
+        <v>2.579510838969094</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.596605068217776</v>
+        <v>-5.35090093248842</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7167475971945474</v>
+        <v>0.8150292514862896</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9105956030749986</v>
+        <v>-0.6584015850708601</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.409388686950406</v>
+        <v>2.560705097752889</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.356174571412915</v>
+        <v>-5.11047043568356</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8146628725413692</v>
+        <v>0.9129445268331113</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6701651062701384</v>
+        <v>-0.4179710882659998</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.5553900616582</v>
+        <v>2.706706472460683</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.283932003241721</v>
+        <v>-5.038227867512365</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8474892136446672</v>
+        <v>0.9457708679364094</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6701651062701384</v>
+        <v>-0.4179710882659998</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.55931937549302</v>
+        <v>2.710635786295503</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.230933680960333</v>
+        <v>-4.985229545230977</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8693671264745624</v>
+        <v>0.9676487807663046</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6148288472681995</v>
+        <v>-0.362634829264061</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.593199714811523</v>
+        <v>2.744516125614006</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.122128795480606</v>
+        <v>-4.87642465975125</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9098871518864464</v>
+        <v>1.008168806178189</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6148288472681995</v>
+        <v>-0.362634829264061</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.590197786031517</v>
+        <v>2.741514196834</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.902107997443595</v>
+        <v>-4.65640386171424</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9994745081118648</v>
+        <v>1.097756162403607</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4736090022002193</v>
+        <v>-0.2214149841960807</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.676508730082919</v>
+        <v>2.827825140885402</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.769240308380318</v>
+        <v>-4.523536172650962</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.068515766538999</v>
+        <v>1.166797420830741</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4736090022002193</v>
+        <v>-0.2214149841960807</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.692402912884742</v>
+        <v>2.843719323687226</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.609725204860948</v>
+        <v>-4.364021069131592</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.133467652387049</v>
+        <v>1.231749306678791</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3140938986808494</v>
+        <v>-0.06189988067671082</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.789257819436666</v>
+        <v>2.940574230239149</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.46505305976121</v>
+        <v>-4.219348924031855</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.201424612988384</v>
+        <v>1.299706267280126</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1694217535811119</v>
+        <v>0.0827722644230266</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.886149209057948</v>
+        <v>3.037465619860432</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.524927887118903</v>
+        <v>-4.279223751389547</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.163512173446733</v>
+        <v>1.261793827738475</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2292965809388041</v>
+        <v>0.02289743706533448</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.836261804044759</v>
+        <v>2.987578214847242</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.438128389339894</v>
+        <v>-4.192424253610538</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.220632465880902</v>
+        <v>1.318914120172645</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2292965809388041</v>
+        <v>0.02289743706533448</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.858662297367325</v>
+        <v>3.009978708169808</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.4405980958017</v>
+        <v>-4.194893960072344</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.219716984669592</v>
+        <v>1.317998638961335</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2317662874006102</v>
+        <v>0.02042773060352832</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.857252874863653</v>
+        <v>3.008569285666137</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.508968282125711</v>
+        <v>-4.263264146396354</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.20337583261469</v>
+        <v>1.301657486906433</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2224905883643953</v>
+        <v>0.02970342963974326</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.873825216760085</v>
+        <v>3.025141627562568</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.617506463041845</v>
+        <v>-4.371802327312488</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.150397268880128</v>
+        <v>1.24867892317187</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2224905883643953</v>
+        <v>0.02970342963974326</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.864261925391976</v>
+        <v>3.015578336194459</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.64849962237055</v>
+        <v>-4.371566918143481</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9627095701890322</v>
+        <v>1.07348265187986</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2224905883643953</v>
+        <v>0.02970342963974326</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.688971490432363</v>
+        <v>2.840287901234846</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.74603895067589</v>
+        <v>3.746038950675891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.473025362578081</v>
+        <v>-4.196092658351011</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.037466506097807</v>
+        <v>1.148239587788636</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2224905883643953</v>
+        <v>0.02970342963974326</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.69353872242415</v>
+        <v>2.844855133226634</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.58396161521933</v>
+        <v>-4.30702891099226</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.968834033802515</v>
+        <v>1.079607115493343</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2224905883643953</v>
+        <v>0.02970342963974326</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.669280751185358</v>
+        <v>2.820597161987841</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.786988192762563</v>
+        <v>-4.510055488535493</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8907547880051272</v>
+        <v>1.001527869695955</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4255171659076287</v>
+        <v>-0.1733231479034901</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.550596189879323</v>
+        <v>2.701912600681806</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.62906259382727</v>
+        <v>-4.3521298896002</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9640974140113769</v>
+        <v>1.074870495702205</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4255171659076287</v>
+        <v>-0.1733231479034901</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.560768576311455</v>
+        <v>2.712084987113939</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.542819130800893</v>
+        <v>-4.265886426573823</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9935410697957883</v>
+        <v>1.104314151486616</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4255171659076287</v>
+        <v>-0.1733231479034901</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.555714846885316</v>
+        <v>2.707031257687799</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.544002215451954</v>
+        <v>-4.267069511224884</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9848436113798893</v>
+        <v>1.095616693070717</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4311602143741402</v>
+        <v>-0.1789661963700017</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.544104793249934</v>
+        <v>2.695421204052417</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.420874508457871</v>
+        <v>-4.143941804230801</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.034646567210624</v>
+        <v>1.145419648901452</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4311602143741402</v>
+        <v>-0.1789661963700017</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.544656666283036</v>
+        <v>2.695973077085519</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.328064027007011</v>
+        <v>-4.051131322779941</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.001043451682333</v>
+        <v>1.111816533373162</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3383497329232809</v>
+        <v>-0.08615571491914231</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.529615647044917</v>
+        <v>2.6809320578474</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.279500974785981</v>
+        <v>-4.002568270558911</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.022342148495346</v>
+        <v>1.133115230186174</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2897866807022507</v>
+        <v>-0.03759266269811212</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.560626954302136</v>
+        <v>2.711943365104619</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.166829756549731</v>
+        <v>-3.88989705232266</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.062486344301569</v>
+        <v>1.173259425992398</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1771154624660005</v>
+        <v>0.07507855553813808</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.623305393755609</v>
+        <v>2.774621804558092</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.054452755367058</v>
+        <v>-3.777520051139988</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.112928440605306</v>
+        <v>1.223701522296134</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1771154624660005</v>
+        <v>0.07507855553813808</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.628796689586276</v>
+        <v>2.78011310038876</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.252687324253789</v>
+        <v>-3.975754620026718</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.045131814819153</v>
+        <v>1.155904896509981</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.375350031352731</v>
+        <v>-0.1231560133485925</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.521353150022777</v>
+        <v>2.67266956082526</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.335688605279068</v>
+        <v>-4.058755901051997</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8502870224096943</v>
+        <v>0.9610601041005227</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3939209158799048</v>
+        <v>-0.1417268978757663</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.348566339307126</v>
+        <v>2.499882750109609</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199263</v>
+        <v>3.682712735199262</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.462755611586056</v>
+        <v>-4.185822907358985</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9196098806061046</v>
+        <v>1.030382962296933</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3939209158799048</v>
+        <v>-0.1417268978757663</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.468716000026332</v>
+        <v>2.620032410828815</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660762</v>
+        <v>3.733008865660761</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.549354194567159</v>
+        <v>-4.272421490340088</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8994834735159865</v>
+        <v>1.010256555206815</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3939209158799048</v>
+        <v>-0.1417268978757663</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.483229026128655</v>
+        <v>2.634545436931138</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383417</v>
+        <v>3.741170494383416</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.510970532009008</v>
+        <v>-4.234037827781937</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9122563798816157</v>
+        <v>1.023029461572444</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3555372533217536</v>
+        <v>-0.1033432353176151</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.503678665005914</v>
+        <v>2.654995075808397</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.333854201973842</v>
+        <v>-4.056921497746771</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9798319407409839</v>
+        <v>1.090605022431812</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3555372533217536</v>
+        <v>-0.1033432353176151</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.500407693851216</v>
+        <v>2.651724104653699</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.304152077997548</v>
+        <v>-4.027219373770477</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9923961820934144</v>
+        <v>1.103169263784243</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.360007378537067</v>
+        <v>-0.1078133605329284</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.498409010483941</v>
+        <v>2.649725421286424</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.12477665675878</v>
+        <v>-3.84784395253171</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.057933325895336</v>
+        <v>1.168706407586164</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2032306203663483</v>
+        <v>0.04896339763779023</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.586262040692787</v>
+        <v>2.73757845149527</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.169790870279387</v>
+        <v>-3.892858166052316</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.020735095818683</v>
+        <v>1.131508177509511</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2335795156809529</v>
+        <v>0.01861450232318562</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.548860158835614</v>
+        <v>2.700176569638097</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.436795380551822</v>
+        <v>-4.159862676324751</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9196248540486547</v>
+        <v>1.030397935739483</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4279425537239015</v>
+        <v>-0.175748535719763</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.43793389834879</v>
+        <v>2.589250309151273</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.725582601010737</v>
+        <v>-4.448649896783667</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8033138877615902</v>
+        <v>0.9140869694524185</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5290286738229019</v>
+        <v>-0.2768346558187633</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.376486148185891</v>
+        <v>2.527802558988375</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.693107014839965</v>
+        <v>-4.416174310612894</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8139040837842157</v>
+        <v>0.9246771654750441</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5290286738229019</v>
+        <v>-0.2768346558187633</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.374086109740208</v>
+        <v>2.525402520542691</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.674068887132668</v>
+        <v>-4.397136182905597</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8180440540753795</v>
+        <v>0.9288171357662078</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5872122851540964</v>
+        <v>-0.3350182671499579</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.335700662149736</v>
+        <v>2.48701707295222</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.705195518283286</v>
+        <v>-4.428262814056215</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9831752705538128</v>
+        <v>1.093948352244641</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5872122851540964</v>
+        <v>-0.3350182671499579</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.513282531088417</v>
+        <v>2.6645989418909</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.757515898884078</v>
+        <v>-4.480583194657007</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9630804472996295</v>
+        <v>1.073853528990458</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5522654251452243</v>
+        <v>-0.3000714071410857</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.535083976079874</v>
+        <v>2.686400386882357</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.901838804808997</v>
+        <v>-4.624906100581926</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9113598153265881</v>
+        <v>1.022132897017416</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5522654251452243</v>
+        <v>-0.3000714071410857</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.5410925064768</v>
+        <v>2.692408917279283</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989899</v>
+        <v>3.7814976749899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.754095834573994</v>
+        <v>-4.477163130346923</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.049609651212611</v>
+        <v>1.160382732903439</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3844580679103411</v>
+        <v>-0.1322640499062026</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.720929568609752</v>
+        <v>2.872245979412235</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224235365116</v>
+        <v>3.802242353651161</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.856110517105216</v>
+        <v>-4.579177812878145</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.011597399731603</v>
+        <v>1.122370481422432</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3844580679103411</v>
+        <v>-0.1322640499062026</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.723723190141233</v>
+        <v>2.875039600943716</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864719</v>
+        <v>3.80560540986472</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.719501173011123</v>
+        <v>-4.442568468784052</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.066903485760899</v>
+        <v>1.177676567451727</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2478487238162486</v>
+        <v>0.004345294187889925</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.806351144989347</v>
+        <v>2.957667555791829</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.862266505833773</v>
+        <v>-4.585333801606702</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.008877829371949</v>
+        <v>1.119650911062777</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.390614056638899</v>
+        <v>-0.1384200386347605</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.719772422035867</v>
+        <v>2.87108883283835</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.799968507057651</v>
+        <v>-4.52303580283058</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.100132582679219</v>
+        <v>1.210905664370047</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.390614056638899</v>
+        <v>-0.1384200386347605</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.786107975832687</v>
+        <v>2.93742438663517</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.598178309392493</v>
+        <v>-4.321245605165422</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8894295341346801</v>
+        <v>1.000202615825508</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1925958644697446</v>
+        <v>0.05959815353439391</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.613499763523578</v>
+        <v>2.764816174326061</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.5382876277499</v>
+        <v>-4.261354923522829</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9836760391138926</v>
+        <v>1.094449120804721</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1327051828271512</v>
+        <v>0.1194888351769874</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.719724404831309</v>
+        <v>2.871040815633792</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789544</v>
+        <v>3.819059724789541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.636028172374874</v>
+        <v>-4.359095468147803</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9592075573799463</v>
+        <v>1.069980639070775</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1485944609601313</v>
+        <v>0.1035995570440072</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.724818574067565</v>
+        <v>2.876134984870048</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.745268518984661</v>
+        <v>3.779929537843628</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.652749136434577</v>
+        <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.636028172374874</v>
+        <v>-4.316037727332986</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9592075573799463</v>
+        <v>1.085739716221373</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1485944609601313</v>
+        <v>0.1292546032480456</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.645812933420945</v>
+        <v>2.890063993417142</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240524.xlsx
+++ b/tame_output/ON/bt/strategyON_20240524.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.2%</t>
+          <t>-600.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-267.6%</t>
+          <t>-270.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-245.1%</t>
+          <t>-293.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-211.1%</t>
+          <t>-217.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-161.0%</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.037856068422343</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7011801242462279</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.072415921171359</v>
+        <v>-1.080348183220266</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.473229423226098</v>
+        <v>2.468470065996753</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.446444845603022</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5365061573887155</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.481004698352038</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.22683770093245</v>
+        <v>2.222078343703105</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.784463377737104</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3964841770065433</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.481004698352038</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.22202313340391</v>
+        <v>2.217263776174566</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.200855252024102</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2279214779006216</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.481004698352038</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.220017184012788</v>
+        <v>2.215257826783443</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.51746719456475</v>
+        <v>-7.48829682740546</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1115353915530415</v>
+        <v>0.1232035384167576</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.481004698352038</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.230275874681467</v>
+        <v>2.225516517452122</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.863342016549559</v>
+        <v>-7.834171649390269</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03071497209518714</v>
+        <v>-0.01904682523147105</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.481004698352038</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.226375439827162</v>
+        <v>2.221616082597818</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.026921894733944</v>
+        <v>-7.997751527574653</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09774200331394001</v>
+        <v>-0.08607385645022392</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.481004698352038</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.224780359882163</v>
+        <v>2.220021002652818</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.323583236544142</v>
+        <v>-8.294412869384852</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2126275641088111</v>
+        <v>-0.200959417245095</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.549747834085916</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.187313454371044</v>
+        <v>2.182554097141699</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.446827625759571</v>
+        <v>-8.417657258600281</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2659516243293858</v>
+        <v>-0.2542834774656697</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.549747834085916</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.18328714983664</v>
+        <v>2.178527792607296</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.829829014502202</v>
+        <v>-8.800658647342912</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4192542811480227</v>
+        <v>-0.4075861342843066</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.549747834085916</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.183185048515056</v>
+        <v>2.178425691285712</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.987227894715323</v>
+        <v>-8.958057527556033</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4796423172618405</v>
+        <v>-0.4679741703981244</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.707146714299037</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.091317236358614</v>
+        <v>2.08655787912927</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.346758217219325</v>
+        <v>-9.317587850060034</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6181041429653913</v>
+        <v>-0.6064359961016752</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.707146714299037</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.096667539656664</v>
+        <v>2.09190818242732</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.397107280673547</v>
+        <v>-9.367936913514257</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6303277483899024</v>
+        <v>-0.6186596015261863</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.757495777753259</v>
+        <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.074374121541308</v>
+        <v>2.069614764311964</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776672</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.494726558094943</v>
+        <v>-9.465556190935652</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6663337087366918</v>
+        <v>-0.6546655618729758</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.855115055174656</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.018844305710239</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.491035633138532</v>
+        <v>-9.461865265979242</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6648573387541279</v>
+        <v>-0.6531891918904118</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.855115055174656</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.018844305710239</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.695293808468396</v>
+        <v>-9.666123441309106</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7410474117674308</v>
+        <v>-0.7293792649037147</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.982753999788645</v>
+        <v>-1.990686261837552</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.947774136060488</v>
+        <v>1.943014778831144</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.837103582675184</v>
+        <v>-9.807933215515893</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.79328876696571</v>
+        <v>-0.781620620101994</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.15403279743422</v>
+        <v>-2.161965059483127</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.849489411957579</v>
+        <v>1.844730054728235</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.763633751007735</v>
+        <v>-9.734463383848444</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7485291328053094</v>
+        <v>-0.7368609859415933</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.080562965766772</v>
+        <v>-2.088495227815679</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.908943012451469</v>
+        <v>1.904183655222125</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.938758168394278</v>
+        <v>-9.909587801234988</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8040236790124098</v>
+        <v>-0.7923555321486937</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.255687383153316</v>
+        <v>-2.263619645202223</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.81842358276706</v>
+        <v>1.813664225537716</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.17321026240877</v>
+        <v>-10.14403989524948</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9050236815198018</v>
+        <v>-0.8933555346560857</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.255687383153316</v>
+        <v>-2.263619645202223</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.811204417865464</v>
+        <v>1.80644506063612</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.46101410694601</v>
+        <v>-10.43184373978672</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.026817410108673</v>
+        <v>-1.015149263244957</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.543491227690554</v>
+        <v>-2.551423489739461</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.631849920369145</v>
+        <v>1.6270905631398</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.51380026254633</v>
+        <v>-10.48462989538704</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.046816082510247</v>
+        <v>-1.035147935646531</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.639166714272951</v>
+        <v>-2.647098976321858</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.575560418258263</v>
+        <v>1.570801061028918</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.74582918228259</v>
+        <v>-10.7166588151233</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.136933921775638</v>
+        <v>-1.125265774911921</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.701179411461374</v>
+        <v>-2.709111673510281</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.541046528574323</v>
+        <v>1.536287171344979</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.69381366831378</v>
+        <v>-10.66464330115449</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.112137380501712</v>
+        <v>-1.100469233637996</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.701179411461374</v>
+        <v>-2.709111673510281</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.545036864260724</v>
+        <v>1.54027750703138</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.8354855100379</v>
+        <v>-10.80631514287861</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.170281344090101</v>
+        <v>-1.158613197226385</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.701179411461374</v>
+        <v>-2.709111673510281</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.543561637361982</v>
+        <v>1.538802280132638</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.78589466561307</v>
+        <v>-10.75672429845378</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.135391596155296</v>
+        <v>-1.12372344929158</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.65158856703654</v>
+        <v>-2.659520829085447</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.588369554181755</v>
+        <v>1.583610196952411</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.58674255837597</v>
+        <v>-10.55757219121668</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.068781886907139</v>
+        <v>-1.057113740043423</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.486266041086727</v>
+        <v>-2.494198303135634</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.67451193610496</v>
+        <v>1.669752578875616</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.36089740565656</v>
+        <v>-10.33172703849727</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.968864752783166</v>
+        <v>-0.957196605919449</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.444339365499563</v>
+        <v>-2.45227162754847</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.709247014493467</v>
+        <v>1.704487657264123</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.23631874931897</v>
+        <v>-10.20714838215967</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9178941456920708</v>
+        <v>-0.9062259988283539</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.444339365499563</v>
+        <v>-2.45227162754847</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.710386159049526</v>
+        <v>1.705626801820182</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.28921403736325</v>
+        <v>-10.26004367020396</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9364184867476775</v>
+        <v>-0.9247503398839605</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.439384019411117</v>
+        <v>-2.447316281460024</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.715993140864701</v>
+        <v>1.711233783635357</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.0053053064345</v>
+        <v>-9.976134939275212</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8171212901375413</v>
+        <v>-0.8054531432738248</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.439384019411117</v>
+        <v>-2.447316281460024</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.721726845103338</v>
+        <v>1.716967487873994</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.933938913824857</v>
+        <v>-9.904768546665565</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7983119954875475</v>
+        <v>-0.786643848623831</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.368017626801469</v>
+        <v>-2.375949888850376</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.754809418275261</v>
+        <v>1.750050061045917</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.670102046620787</v>
+        <v>-9.640931679461495</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7026607299188274</v>
+        <v>-0.6909925830551105</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.368017626801469</v>
+        <v>-2.375949888850376</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.744925936962354</v>
+        <v>1.740166579733009</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.40286024575239</v>
+        <v>-9.373689878593098</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5975985700708422</v>
+        <v>-0.5859304232071252</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.368017626801469</v>
+        <v>-2.375949888850376</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.74309137646298</v>
+        <v>1.738332019233636</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.304953207075899</v>
+        <v>-9.275782839916607</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5587360695737065</v>
+        <v>-0.5470679227099899</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.300031876940912</v>
+        <v>-2.30796413898982</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.783582511405853</v>
+        <v>1.778823154176509</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.280999666099941</v>
+        <v>-9.251829298940649</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5484861470378299</v>
+        <v>-0.536818000174113</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.276078335964955</v>
+        <v>-2.284010598013862</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.798623142136921</v>
+        <v>1.793863784907577</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487765</v>
+        <v>3.789307536487767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.016939727777144</v>
+        <v>-8.987769360617852</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4561224878704633</v>
+        <v>-0.4444543410067463</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.012018397642159</v>
+        <v>-2.019950659691066</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.943798788968847</v>
+        <v>1.939039431739502</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.309860104272307</v>
+        <v>-8.280689737113015</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1760776721288293</v>
+        <v>-0.1644095252651123</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.012018397642159</v>
+        <v>-2.019950659691066</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.941011755308546</v>
+        <v>1.936252398079201</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858721</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.269675805906116</v>
+        <v>-8.240505438746824</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1596603288945118</v>
+        <v>-0.1479921820307948</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.971834099275968</v>
+        <v>-1.979766361324875</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.965465958216102</v>
+        <v>1.960706600986757</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096466</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.189606010368312</v>
+        <v>-8.16043564320902</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1282655894586329</v>
+        <v>-0.1165974425949159</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.891764303738164</v>
+        <v>-1.899696565787071</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.012874656759541</v>
+        <v>2.008115299530197</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.956124788138713</v>
+        <v>-7.926954420979421</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.02694867172894089</v>
+        <v>-0.01528052486522435</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.658283081508566</v>
+        <v>-1.666215343557473</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.160887818935152</v>
+        <v>2.156128461705808</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.806458397131198</v>
+        <v>-7.777288029971906</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.03002567436110581</v>
+        <v>0.04169382122482279</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.56537959026603</v>
+        <v>-1.573311852314937</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.213737703367715</v>
+        <v>2.208978346138371</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.674182923500312</v>
+        <v>-7.64501255634102</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.07830335056048732</v>
+        <v>0.08997149742420429</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.433104116635143</v>
+        <v>-1.44103637868405</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.288470474293274</v>
+        <v>2.283711117063929</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.483583248827159</v>
+        <v>-7.454412881667867</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1573582811173853</v>
+        <v>0.1690264279811018</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.24250444196199</v>
+        <v>-1.250436704010897</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.405645339784802</v>
+        <v>2.400885982555458</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.234583450143578</v>
+        <v>-7.205413082984286</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2698645418144765</v>
+        <v>0.281532688678193</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.24250444196199</v>
+        <v>-1.250436704010897</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.418551681008461</v>
+        <v>2.413792323779117</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.340173439916683</v>
+        <v>-7.311003072757391</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.09965261630601585</v>
+        <v>0.1113207631697328</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.348094431735094</v>
+        <v>-1.356026693784002</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.22722175754538</v>
+        <v>2.222462400316036</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.35890834203528</v>
+        <v>-7.329737974875988</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1407029973356635</v>
+        <v>0.15237114419938</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.348094431735094</v>
+        <v>-1.356026693784002</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.275766099422466</v>
+        <v>2.271006742193122</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.21096830062768</v>
+        <v>-7.181797933468388</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.08000009121053564</v>
+        <v>0.09166823807425217</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.327773515826537</v>
+        <v>-1.335705777875444</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.168079726279433</v>
+        <v>2.163320369050089</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.193810150496386</v>
+        <v>-7.164639783337094</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07814936500957526</v>
+        <v>0.08981751187329179</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.310615365695243</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.169660630104731</v>
+        <v>2.164901272875387</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.150261743725696</v>
+        <v>-7.121091376566404</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08860811562275828</v>
+        <v>0.1002762624864748</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.310615365695243</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.162700018009638</v>
+        <v>2.157940660780294</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.908113350271837</v>
+        <v>-6.878942983112545</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1999298273854446</v>
+        <v>0.2115979742491612</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.310615365695243</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.177162372390781</v>
+        <v>2.172403015161437</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.844883978503489</v>
+        <v>-6.815713611344197</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2197536965519786</v>
+        <v>0.2314218434156956</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.310615365695243</v>
+        <v>-1.31854762774415</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.171694492849976</v>
+        <v>2.166935135620632</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.721592843686358</v>
+        <v>-6.692422476527066</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2665682444894082</v>
+        <v>0.2782363913531247</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.187324230878112</v>
+        <v>-1.195256492927019</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.243167267750832</v>
+        <v>2.238407910521488</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.700443644782915</v>
+        <v>-6.671273277623623</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2827289022881105</v>
+        <v>0.2943970491518275</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.166175031974669</v>
+        <v>-1.174107294023576</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.263557765330223</v>
+        <v>2.258798408100879</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.456678202799471</v>
+        <v>-6.427507835640179</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.376015787428539</v>
+        <v>0.3876839342922556</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.166175031974669</v>
+        <v>-1.174107294023576</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.259338473677274</v>
+        <v>2.254579116447929</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.3097811750816</v>
+        <v>-6.280610807922308</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4368989124357032</v>
+        <v>0.4485670592994202</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.118516789996081</v>
+        <v>-1.126449052044988</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.290057732784442</v>
+        <v>2.285298375555098</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.059930781132525</v>
+        <v>-6.030760413973233</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5295811449990353</v>
+        <v>0.5412492918627518</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.118516789996081</v>
+        <v>-1.126449052044988</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.282799807768145</v>
+        <v>2.2780404505388</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.884038688665093</v>
+        <v>-5.854868321505801</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.603537105506657</v>
+        <v>0.6152052523703735</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.118516789996081</v>
+        <v>-1.126449052044988</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.286398931288793</v>
+        <v>2.281639574059449</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.71259222564263</v>
+        <v>-5.683421858483338</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6854431967701959</v>
+        <v>0.6971113436339129</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9470703269736175</v>
+        <v>-0.9550025890225248</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.402594315156825</v>
+        <v>2.39783495792748</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.487559225973807</v>
+        <v>-5.458388858814515</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.774476874254022</v>
+        <v>0.786145021117739</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7220373273047946</v>
+        <v>-0.7299695893537019</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.536634592574416</v>
+        <v>2.531875235345071</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.423923483739872</v>
+        <v>-5.39475311658058</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8046259722019133</v>
+        <v>0.8162941190656299</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6584015850708601</v>
+        <v>-0.6663338471197674</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.579510838969094</v>
+        <v>2.574751481739749</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.35090093248842</v>
+        <v>-5.301753075374682</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8150292514862896</v>
+        <v>0.8346883943317849</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6584015850708601</v>
+        <v>-0.6663338471197674</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.560705097752889</v>
+        <v>2.555945740523545</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.11047043568356</v>
+        <v>-5.061322578569822</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9129445268331113</v>
+        <v>0.9326036696786062</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4179710882659998</v>
+        <v>-0.4259033503149071</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.706706472460683</v>
+        <v>2.701947115231338</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.038227867512365</v>
+        <v>-4.989080010398627</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9457708679364094</v>
+        <v>0.9654300107819045</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4179710882659998</v>
+        <v>-0.4259033503149071</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.710635786295503</v>
+        <v>2.705876429066159</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.822323422349961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.985229545230977</v>
+        <v>-4.936081688117239</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9676487807663046</v>
+        <v>0.9873079236117996</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.362634829264061</v>
+        <v>-0.3705670913129683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.744516125614006</v>
+        <v>2.739756768384662</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.87642465975125</v>
+        <v>-4.841322102916728</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.008168806178189</v>
+        <v>1.022209828911997</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.362634829264061</v>
+        <v>-0.3705670913129683</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.741514196834</v>
+        <v>2.736754839604655</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.65640386171424</v>
+        <v>-4.621301304879718</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.097756162403607</v>
+        <v>1.111797185137416</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2214149841960807</v>
+        <v>-0.229347246244988</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.827825140885402</v>
+        <v>2.823065783656058</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.523536172650962</v>
+        <v>-4.48843361581644</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.166797420830741</v>
+        <v>1.18083844356455</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2214149841960807</v>
+        <v>-0.229347246244988</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.843719323687226</v>
+        <v>2.838959966457881</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.364021069131592</v>
+        <v>-4.32891851229707</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.231749306678791</v>
+        <v>1.2457903294126</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06189988067671082</v>
+        <v>-0.06983214272561811</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.940574230239149</v>
+        <v>2.935814873009805</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.219348924031855</v>
+        <v>-4.184246367197333</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.299706267280126</v>
+        <v>1.313747290013935</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.0827722644230266</v>
+        <v>0.07484000237411931</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.037465619860432</v>
+        <v>3.032706262631087</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.279223751389547</v>
+        <v>-4.244121194555025</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.261793827738475</v>
+        <v>1.275834850472284</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.02289743706533448</v>
+        <v>0.01496517501642719</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.987578214847242</v>
+        <v>2.982818857617898</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.192424253610538</v>
+        <v>-4.157321696776016</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.318914120172645</v>
+        <v>1.332955142906453</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.02289743706533448</v>
+        <v>0.01496517501642719</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.009978708169808</v>
+        <v>3.005219350940464</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.194893960072344</v>
+        <v>-4.159791403237822</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.317998638961335</v>
+        <v>1.332039661695143</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.02042773060352832</v>
+        <v>0.01249546855462103</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.008569285666137</v>
+        <v>3.003809928436792</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.263264146396354</v>
+        <v>-4.228161589561832</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.301657486906433</v>
+        <v>1.315698509640241</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02970342963974326</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.025141627562568</v>
+        <v>3.020382270333223</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.371802327312488</v>
+        <v>-4.336699770477966</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.24867892317187</v>
+        <v>1.262719945905679</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02970342963974326</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.015578336194459</v>
+        <v>3.010818978965114</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.371566918143481</v>
+        <v>-4.367692929806672</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.07348265187986</v>
+        <v>1.075032247214584</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02970342963974326</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.840287901234846</v>
+        <v>2.835528544005501</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.196092658351011</v>
+        <v>-4.192218670014203</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.148239587788636</v>
+        <v>1.149789183123359</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02970342963974326</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.844855133226634</v>
+        <v>2.840095775997289</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695436</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.30702891099226</v>
+        <v>-4.303154922655452</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.079607115493343</v>
+        <v>1.081156710828066</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02970342963974326</v>
+        <v>0.02177116759083597</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.820597161987841</v>
+        <v>2.815837804758496</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.510055488535493</v>
+        <v>-4.506181500198685</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.001527869695955</v>
+        <v>1.003077465030679</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1733231479034901</v>
+        <v>-0.1812554099523974</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.701912600681806</v>
+        <v>2.697153243452462</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.3521298896002</v>
+        <v>-4.348255901263392</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.074870495702205</v>
+        <v>1.076420091036928</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1733231479034901</v>
+        <v>-0.1812554099523974</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.712084987113939</v>
+        <v>2.707325629884594</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.265886426573823</v>
+        <v>-4.262012438237014</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.104314151486616</v>
+        <v>1.10586374682134</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1733231479034901</v>
+        <v>-0.1812554099523974</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.707031257687799</v>
+        <v>2.702271900458455</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.267069511224884</v>
+        <v>-4.263195522888076</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.095616693070717</v>
+        <v>1.097166288405441</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1789661963700017</v>
+        <v>-0.186898458418909</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.695421204052417</v>
+        <v>2.690661846823073</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273186</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.143941804230801</v>
+        <v>-4.140067815893993</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.145419648901452</v>
+        <v>1.146969244236175</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1789661963700017</v>
+        <v>-0.186898458418909</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.695973077085519</v>
+        <v>2.691213719856175</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.051131322779941</v>
+        <v>-4.047257334443133</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.111816533373162</v>
+        <v>1.113366128707885</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08615571491914231</v>
+        <v>-0.0940879769680496</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.6809320578474</v>
+        <v>2.676172700618056</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030423</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.002568270558911</v>
+        <v>-3.998694282222103</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.133115230186174</v>
+        <v>1.134664825520898</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.03759266269811212</v>
+        <v>-0.04552492474701941</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.711943365104619</v>
+        <v>2.707184007875275</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942735</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.88989705232266</v>
+        <v>-3.886023063985852</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.173259425992398</v>
+        <v>1.174809021327121</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07507855553813808</v>
+        <v>0.06714629348923079</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.774621804558092</v>
+        <v>2.769862447328748</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268533</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.777520051139988</v>
+        <v>-3.77364606280318</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.223701522296134</v>
+        <v>1.225251117630857</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07507855553813808</v>
+        <v>0.06714629348923079</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.78011310038876</v>
+        <v>2.775353743159415</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.975754620026718</v>
+        <v>-3.97188063168991</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.155904896509981</v>
+        <v>1.157454491844704</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1231560133485925</v>
+        <v>-0.1310882753974998</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.67266956082526</v>
+        <v>2.667910203595916</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175317</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.058755901051997</v>
+        <v>-4.054881912715189</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9610601041005227</v>
+        <v>0.962609699435246</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1417268978757663</v>
+        <v>-0.1496591599246735</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.499882750109609</v>
+        <v>2.495123392880265</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199262</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.185822907358985</v>
+        <v>-4.181948919022177</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.030382962296933</v>
+        <v>1.031932557631656</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1417268978757663</v>
+        <v>-0.1496591599246735</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.620032410828815</v>
+        <v>2.61527305359947</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660761</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.272421490340088</v>
+        <v>-4.26854750200328</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.010256555206815</v>
+        <v>1.011806150541538</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1417268978757663</v>
+        <v>-0.1496591599246735</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.634545436931138</v>
+        <v>2.629786079701793</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383416</v>
+        <v>3.741170494383419</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.234037827781937</v>
+        <v>-4.230163839445129</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.023029461572444</v>
+        <v>1.024579056907167</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1033432353176151</v>
+        <v>-0.1112754973665224</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.654995075808397</v>
+        <v>2.650235718579053</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002477</v>
+        <v>3.75114362200248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.056921497746771</v>
+        <v>-4.053047509409963</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.090605022431812</v>
+        <v>1.092154617766536</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1033432353176151</v>
+        <v>-0.1112754973665224</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.651724104653699</v>
+        <v>2.646964747424355</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263894</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.027219373770477</v>
+        <v>-4.023345385433669</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.103169263784243</v>
+        <v>1.104718859118966</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1078133605329284</v>
+        <v>-0.1157456225818357</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.649725421286424</v>
+        <v>2.64496606405708</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481225</v>
+        <v>3.750725801481229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.84784395253171</v>
+        <v>-3.843969964194901</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.168706407586164</v>
+        <v>1.170256002920888</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04896339763779023</v>
+        <v>0.04103113558888294</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.73757845149527</v>
+        <v>2.732819094265925</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452221</v>
+        <v>3.716988143452225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.892858166052316</v>
+        <v>-3.888984177715507</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.131508177509511</v>
+        <v>1.133057772844235</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01861450232318562</v>
+        <v>0.01068224027427833</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.700176569638097</v>
+        <v>2.695417212408752</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979527</v>
+        <v>3.737023032979532</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.159862676324751</v>
+        <v>-4.155988687987943</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.030397935739483</v>
+        <v>1.031947531074207</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.175748535719763</v>
+        <v>-0.1836807977686702</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.589250309151273</v>
+        <v>2.584490951921929</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230803</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.448649896783667</v>
+        <v>-4.444775908446858</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9140869694524185</v>
+        <v>0.9156365647871418</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2768346558187633</v>
+        <v>-0.2847669178676706</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.527802558988375</v>
+        <v>2.52304320175903</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285449</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.416174310612894</v>
+        <v>-4.412300322276086</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9246771654750441</v>
+        <v>0.9262267608097674</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2768346558187633</v>
+        <v>-0.2847669178676706</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.525402520542691</v>
+        <v>2.520643163313347</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.397136182905597</v>
+        <v>-4.393262194568789</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9288171357662078</v>
+        <v>0.9303667311009312</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3350182671499579</v>
+        <v>-0.3429505291988652</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.48701707295222</v>
+        <v>2.482257715722875</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.428262814056215</v>
+        <v>-4.424388825719407</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.093948352244641</v>
+        <v>1.095497947579364</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3350182671499579</v>
+        <v>-0.3429505291988652</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.6645989418909</v>
+        <v>2.659839584661556</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537859</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.480583194657007</v>
+        <v>-4.476709206320199</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.073853528990458</v>
+        <v>1.075403124325181</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3000714071410857</v>
+        <v>-0.308003669189993</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.686400386882357</v>
+        <v>2.681641029653012</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259115</v>
+        <v>3.787422005259119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.624906100581926</v>
+        <v>-4.621032112245118</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.022132897017416</v>
+        <v>1.02368249235214</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3000714071410857</v>
+        <v>-0.308003669189993</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.692408917279283</v>
+        <v>2.687649560049938</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.7814976749899</v>
+        <v>3.781497674989904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.477163130346923</v>
+        <v>-4.473289142010115</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.160382732903439</v>
+        <v>1.161932328238163</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1322640499062026</v>
+        <v>-0.1401963119551098</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.872245979412235</v>
+        <v>2.86748662218289</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651161</v>
+        <v>3.802242353651166</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.579177812878145</v>
+        <v>-4.575303824541336</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.122370481422432</v>
+        <v>1.123920076757155</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1322640499062026</v>
+        <v>-0.1401963119551098</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.875039600943716</v>
+        <v>2.870280243714371</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560540986472</v>
+        <v>3.805605409864725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.442568468784052</v>
+        <v>-4.438694480447244</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.177676567451727</v>
+        <v>1.17922616278645</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.004345294187889925</v>
+        <v>-0.003586967861017365</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.957667555791829</v>
+        <v>2.952908198562485</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360607</v>
+        <v>3.798236219360612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.585333801606702</v>
+        <v>-4.581459813269894</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.119650911062777</v>
+        <v>1.121200506397501</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1384200386347605</v>
+        <v>-0.1463523006836678</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.87108883283835</v>
+        <v>2.866329475609005</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268418</v>
+        <v>3.867359061268422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.52303580283058</v>
+        <v>-4.519161814493772</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.210905664370047</v>
+        <v>1.21245525970477</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1384200386347605</v>
+        <v>-0.1463523006836678</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.93742438663517</v>
+        <v>2.932665029405826</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462182</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.321245605165422</v>
+        <v>-4.317371616828614</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.000202615825508</v>
+        <v>1.001752211160232</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.05959815353439391</v>
+        <v>0.05166589148548661</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.764816174326061</v>
+        <v>2.760056817096717</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322415</v>
+        <v>3.841441242322419</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.261354923522829</v>
+        <v>-4.313102990904766</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.094449120804721</v>
+        <v>1.073749893851946</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1194888351769874</v>
+        <v>0.05593451740933397</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.871040815633792</v>
+        <v>2.8329082249732</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789541</v>
+        <v>3.851552675441658</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.359095468147803</v>
+        <v>-4.41084353552974</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.069980639070775</v>
+        <v>1.049281412118</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1035995570440072</v>
+        <v>0.04004523927635378</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.876134984870048</v>
+        <v>2.838002394209456</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.779929537843628</v>
+        <v>3.807013631467131</v>
       </c>
       <c r="C1974" t="n">
         <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.316037727332986</v>
+        <v>-4.387997330587224</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.085739716221373</v>
+        <v>1.056955874919678</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.1292546032480456</v>
+        <v>0.06289144421887088</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.890063993417142</v>
+        <v>2.850246097999638</v>
       </c>
     </row>
   </sheetData>
